--- a/AdditionalData/Tables/pyramid_row Keops_100_straight.xlsx
+++ b/AdditionalData/Tables/pyramid_row Keops_100_straight.xlsx
@@ -46,22 +46,22 @@
     <t xml:space="preserve">distance blocks Horiz (Km)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sum force blocks (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum Vert. force blocks (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum Horiz. force blocks (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vert. force blocks row (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horiz. force blocks row (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total force blocks row (GJ)</t>
+    <t xml:space="preserve">Sum force blocks (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum Vert. force blocks (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum Horiz. force blocks (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vert. force blocks row (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horiz. force blocks row (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total force blocks row (MJ)</t>
   </si>
   <si>
     <t xml:space="preserve">% Decrement blocks</t>
@@ -919,6 +919,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -978,8 +979,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1109,5365 +1114,5365 @@
   <dimension ref="A1:Q102"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="23.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="23.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="19.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="24.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="25.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="23.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="24.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="23.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="18.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="18.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="15.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="23.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="23.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="19.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="24.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="25.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="23.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="24.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="23.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="18.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="18.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="15.76"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>32902</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="C2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>4521629</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>4521629</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2" s="1" t="n">
         <v>70198090</v>
       </c>
-      <c r="J2" s="0" t="n">
+      <c r="J2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="K2" s="1" t="n">
         <v>70198090</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="L2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="0" t="n">
+      <c r="M2" s="1" t="n">
         <v>70198090</v>
       </c>
-      <c r="N2" s="0" t="n">
+      <c r="N2" s="1" t="n">
         <v>70198090</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>32591</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>4785164</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>333446</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="1" t="n">
         <v>4451718</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="I3" s="1" t="n">
         <v>145050700</v>
       </c>
-      <c r="J3" s="0" t="n">
+      <c r="J3" s="1" t="n">
         <v>5697030</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3" s="1" t="n">
         <v>139354700</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3" s="1" t="n">
         <v>5697030</v>
       </c>
-      <c r="M3" s="0" t="n">
+      <c r="M3" s="1" t="n">
         <v>69156480</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3" s="1" t="n">
         <v>74852670</v>
       </c>
-      <c r="O3" s="0" t="n">
+      <c r="O3" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="P3" s="0" t="s">
+      <c r="P3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Q3" s="0" t="s">
+      <c r="Q3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>32282</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>5042016</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>659536</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <v>4382479</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="1" t="n">
         <v>224442200</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4" s="1" t="n">
         <v>16973150</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4" s="1" t="n">
         <v>207479800</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4" s="1" t="n">
         <v>11268370</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M4" s="1" t="n">
         <v>68125080</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="1" t="n">
         <v>79391770</v>
       </c>
-      <c r="O4" s="0" t="n">
+      <c r="O4" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="P4" s="0" t="s">
+      <c r="P4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q4" s="0" t="s">
+      <c r="Q4" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>31974</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>5292339</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="1" t="n">
         <v>978725</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="1" t="n">
         <v>4313615</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I5" s="1" t="n">
         <v>308258800</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="J5" s="1" t="n">
         <v>33705840</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5" s="1" t="n">
         <v>274584100</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5" s="1" t="n">
         <v>16708190</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M5" s="1" t="n">
         <v>67104220</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="1" t="n">
         <v>83816700</v>
       </c>
-      <c r="O5" s="0" t="n">
+      <c r="O5" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="P5" s="0" t="s">
+      <c r="P5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q5" s="0" t="s">
+      <c r="Q5" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>31667</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="0" t="s">
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>5536160</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <v>1289895</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="1" t="n">
         <v>4246265</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6" s="1" t="n">
         <v>396386800</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6" s="1" t="n">
         <v>55768040</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" s="1" t="n">
         <v>340676900</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="1" t="n">
         <v>22038180</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6" s="1" t="n">
         <v>66093400</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="1" t="n">
         <v>88128720</v>
       </c>
-      <c r="O6" s="0" t="n">
+      <c r="O6" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="P6" s="0" t="s">
+      <c r="P6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="0" t="s">
+      <c r="Q6" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>31363</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="0" t="s">
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>5831258</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <v>1612165</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <v>4219093</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>489332300</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J7" s="1" t="n">
         <v>83280910</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7" s="1" t="n">
         <v>406079000</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7" s="1" t="n">
         <v>27533040</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7" s="1" t="n">
         <v>65401890</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="1" t="n">
         <v>92946270</v>
       </c>
-      <c r="O7" s="0" t="n">
+      <c r="O7" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="P7" s="0" t="s">
+      <c r="P7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Q7" s="0" t="s">
+      <c r="Q7" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>31059</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="0" t="s">
+      <c r="C8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>6065273</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="1" t="n">
         <v>1913928</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="1" t="n">
         <v>4151345</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>586423700</v>
       </c>
-      <c r="J8" s="0" t="n">
+      <c r="J8" s="1" t="n">
         <v>115875100</v>
       </c>
-      <c r="K8" s="0" t="n">
+      <c r="K8" s="1" t="n">
         <v>470487300</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="L8" s="1" t="n">
         <v>32674160</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8" s="1" t="n">
         <v>64408380</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8" s="1" t="n">
         <v>97091130</v>
       </c>
-      <c r="O8" s="0" t="n">
+      <c r="O8" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="P8" s="0" t="s">
+      <c r="P8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="Q8" s="0" t="s">
+      <c r="Q8" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>30757</v>
       </c>
-      <c r="C9" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="0" t="s">
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>6292928</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="1" t="n">
         <v>2207037</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="1" t="n">
         <v>4085891</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>687549400</v>
       </c>
-      <c r="J9" s="0" t="n">
+      <c r="J9" s="1" t="n">
         <v>153575600</v>
       </c>
-      <c r="K9" s="0" t="n">
+      <c r="K9" s="1" t="n">
         <v>533912200</v>
       </c>
-      <c r="L9" s="0" t="n">
+      <c r="L9" s="1" t="n">
         <v>37693570</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="M9" s="1" t="n">
         <v>63424950</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9" s="1" t="n">
         <v>101125200</v>
       </c>
-      <c r="O9" s="0" t="n">
+      <c r="O9" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="P9" s="0" t="s">
+      <c r="P9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q9" s="0" t="s">
+      <c r="Q9" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>30457</v>
       </c>
-      <c r="C10" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="0" t="s">
+      <c r="C10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>6514270</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <v>2493481</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="1" t="n">
         <v>4020789</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>792598300</v>
       </c>
-      <c r="J10" s="0" t="n">
+      <c r="J10" s="1" t="n">
         <v>196225200</v>
       </c>
-      <c r="K10" s="0" t="n">
+      <c r="K10" s="1" t="n">
         <v>596364300</v>
       </c>
-      <c r="L10" s="0" t="n">
+      <c r="L10" s="1" t="n">
         <v>42601560</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="M10" s="1" t="n">
         <v>62451650</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10" s="1" t="n">
         <v>105049200</v>
       </c>
-      <c r="O10" s="0" t="n">
+      <c r="O10" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="P10" s="0" t="s">
+      <c r="P10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Q10" s="0" t="s">
+      <c r="Q10" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>30158</v>
       </c>
-      <c r="C11" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="0" t="s">
+      <c r="C11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="1" t="n">
         <v>6729322</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="1" t="n">
         <v>2772972</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="1" t="n">
         <v>3956350</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <v>901463600</v>
       </c>
-      <c r="J11" s="0" t="n">
+      <c r="J11" s="1" t="n">
         <v>243845300</v>
       </c>
-      <c r="K11" s="0" t="n">
+      <c r="K11" s="1" t="n">
         <v>657851900</v>
       </c>
-      <c r="L11" s="0" t="n">
+      <c r="L11" s="1" t="n">
         <v>47372540</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="M11" s="1" t="n">
         <v>61488320</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11" s="1" t="n">
         <v>108864400</v>
       </c>
-      <c r="O11" s="0" t="n">
+      <c r="O11" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="P11" s="0" t="s">
+      <c r="P11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Q11" s="0" t="s">
+      <c r="Q11" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>29861</v>
       </c>
-      <c r="C12" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="0" t="s">
+      <c r="C12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <v>6938209</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="1" t="n">
         <v>3045759</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" s="1" t="n">
         <v>3892450</v>
       </c>
-      <c r="I12" s="0" t="n">
+      <c r="I12" s="1" t="n">
         <v>1014036000</v>
       </c>
-      <c r="J12" s="0" t="n">
+      <c r="J12" s="1" t="n">
         <v>295823100</v>
       </c>
-      <c r="K12" s="0" t="n">
+      <c r="K12" s="1" t="n">
         <v>718386600</v>
       </c>
-      <c r="L12" s="0" t="n">
+      <c r="L12" s="1" t="n">
         <v>52018160</v>
       </c>
-      <c r="M12" s="0" t="n">
+      <c r="M12" s="1" t="n">
         <v>60534680</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="1" t="n">
         <v>112571700</v>
       </c>
-      <c r="O12" s="0" t="n">
+      <c r="O12" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="P12" s="0" t="s">
+      <c r="P12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Q12" s="0" t="s">
+      <c r="Q12" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>29564</v>
       </c>
-      <c r="C13" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="0" t="s">
+      <c r="C13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="1" t="n">
         <v>7140959</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="G13" s="1" t="n">
         <v>3312960</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13" s="1" t="n">
         <v>3827999</v>
       </c>
-      <c r="I13" s="0" t="n">
+      <c r="I13" s="1" t="n">
         <v>1130207000</v>
       </c>
-      <c r="J13" s="0" t="n">
+      <c r="J13" s="1" t="n">
         <v>352048800</v>
       </c>
-      <c r="K13" s="0" t="n">
+      <c r="K13" s="1" t="n">
         <v>777978300</v>
       </c>
-      <c r="L13" s="0" t="n">
+      <c r="L13" s="1" t="n">
         <v>56587480</v>
       </c>
-      <c r="M13" s="0" t="n">
+      <c r="M13" s="1" t="n">
         <v>59591270</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13" s="1" t="n">
         <v>116172100</v>
       </c>
-      <c r="O13" s="0" t="n">
+      <c r="O13" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="P13" s="0" t="s">
+      <c r="P13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="Q13" s="0" t="s">
+      <c r="Q13" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>29270</v>
       </c>
-      <c r="C14" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="0" t="s">
+      <c r="C14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="1" t="n">
         <v>7416482</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="G14" s="1" t="n">
         <v>3614531</v>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="H14" s="1" t="n">
         <v>3801952</v>
       </c>
-      <c r="I14" s="0" t="n">
+      <c r="I14" s="1" t="n">
         <v>1250878000</v>
       </c>
-      <c r="J14" s="0" t="n">
+      <c r="J14" s="1" t="n">
         <v>414090900</v>
       </c>
-      <c r="K14" s="0" t="n">
+      <c r="K14" s="1" t="n">
         <v>836924400</v>
       </c>
-      <c r="L14" s="0" t="n">
+      <c r="L14" s="1" t="n">
         <v>61710240</v>
       </c>
-      <c r="M14" s="0" t="n">
+      <c r="M14" s="1" t="n">
         <v>58946180</v>
       </c>
-      <c r="N14" s="0" t="n">
+      <c r="N14" s="1" t="n">
         <v>120670700</v>
       </c>
-      <c r="O14" s="0" t="n">
+      <c r="O14" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="P14" s="0" t="s">
+      <c r="P14" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="Q14" s="0" t="s">
+      <c r="Q14" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>28977</v>
       </c>
-      <c r="C15" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="0" t="s">
+      <c r="C15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="1" t="n">
         <v>7609917</v>
       </c>
-      <c r="G15" s="0" t="n">
+      <c r="G15" s="1" t="n">
         <v>3868614</v>
       </c>
-      <c r="H15" s="0" t="n">
+      <c r="H15" s="1" t="n">
         <v>3741303</v>
       </c>
-      <c r="I15" s="0" t="n">
+      <c r="I15" s="1" t="n">
         <v>1374991000</v>
       </c>
-      <c r="J15" s="0" t="n">
+      <c r="J15" s="1" t="n">
         <v>480204600</v>
       </c>
-      <c r="K15" s="0" t="n">
+      <c r="K15" s="1" t="n">
         <v>894943800</v>
       </c>
-      <c r="L15" s="0" t="n">
+      <c r="L15" s="1" t="n">
         <v>66107380</v>
       </c>
-      <c r="M15" s="0" t="n">
+      <c r="M15" s="1" t="n">
         <v>58019180</v>
       </c>
-      <c r="N15" s="0" t="n">
+      <c r="N15" s="1" t="n">
         <v>124112300</v>
       </c>
-      <c r="O15" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P15" s="0" t="s">
+      <c r="O15" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="Q15" s="0" t="s">
+      <c r="Q15" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>28686</v>
       </c>
-      <c r="C16" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="0" t="s">
+      <c r="C16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="F16" s="1" t="n">
         <v>7797331</v>
       </c>
-      <c r="G16" s="0" t="n">
+      <c r="G16" s="1" t="n">
         <v>4118245</v>
       </c>
-      <c r="H16" s="0" t="n">
+      <c r="H16" s="1" t="n">
         <v>3679086</v>
       </c>
-      <c r="I16" s="0" t="n">
+      <c r="I16" s="1" t="n">
         <v>1502439000</v>
       </c>
-      <c r="J16" s="0" t="n">
+      <c r="J16" s="1" t="n">
         <v>550282300</v>
       </c>
-      <c r="K16" s="0" t="n">
+      <c r="K16" s="1" t="n">
         <v>952045900</v>
       </c>
-      <c r="L16" s="0" t="n">
+      <c r="L16" s="1" t="n">
         <v>70336180</v>
       </c>
-      <c r="M16" s="0" t="n">
+      <c r="M16" s="1" t="n">
         <v>57102130</v>
       </c>
-      <c r="N16" s="0" t="n">
+      <c r="N16" s="1" t="n">
         <v>127449200</v>
       </c>
-      <c r="O16" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P16" s="0" t="s">
+      <c r="O16" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P16" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="Q16" s="0" t="s">
+      <c r="Q16" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>28395</v>
       </c>
-      <c r="C17" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="0" t="s">
+      <c r="C17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17" s="1" t="n">
         <v>7978793</v>
       </c>
-      <c r="G17" s="0" t="n">
+      <c r="G17" s="1" t="n">
         <v>4361106</v>
       </c>
-      <c r="H17" s="0" t="n">
+      <c r="H17" s="1" t="n">
         <v>3617687</v>
       </c>
-      <c r="I17" s="0" t="n">
+      <c r="I17" s="1" t="n">
         <v>1633119000</v>
       </c>
-      <c r="J17" s="0" t="n">
+      <c r="J17" s="1" t="n">
         <v>625153200</v>
       </c>
-      <c r="K17" s="0" t="n">
+      <c r="K17" s="1" t="n">
         <v>1008241000</v>
       </c>
-      <c r="L17" s="0" t="n">
+      <c r="L17" s="1" t="n">
         <v>74490580</v>
       </c>
-      <c r="M17" s="0" t="n">
+      <c r="M17" s="1" t="n">
         <v>56194680</v>
       </c>
-      <c r="N17" s="0" t="n">
+      <c r="N17" s="1" t="n">
         <v>130682400</v>
       </c>
-      <c r="O17" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P17" s="0" t="s">
+      <c r="O17" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P17" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Q17" s="0" t="s">
+      <c r="Q17" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>28107</v>
       </c>
-      <c r="C18" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="0" t="s">
+      <c r="C18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="0" t="n">
+      <c r="F18" s="1" t="n">
         <v>8154324</v>
       </c>
-      <c r="G18" s="0" t="n">
+      <c r="G18" s="1" t="n">
         <v>4595599</v>
       </c>
-      <c r="H18" s="0" t="n">
+      <c r="H18" s="1" t="n">
         <v>3558725</v>
       </c>
-      <c r="I18" s="0" t="n">
+      <c r="I18" s="1" t="n">
         <v>1766930000</v>
       </c>
-      <c r="J18" s="0" t="n">
+      <c r="J18" s="1" t="n">
         <v>702840100</v>
       </c>
-      <c r="K18" s="0" t="n">
+      <c r="K18" s="1" t="n">
         <v>1063537000</v>
       </c>
-      <c r="L18" s="0" t="n">
+      <c r="L18" s="1" t="n">
         <v>78515660</v>
       </c>
-      <c r="M18" s="0" t="n">
+      <c r="M18" s="1" t="n">
         <v>55296920</v>
       </c>
-      <c r="N18" s="0" t="n">
+      <c r="N18" s="1" t="n">
         <v>133812900</v>
       </c>
-      <c r="O18" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P18" s="0" t="s">
+      <c r="O18" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P18" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="Q18" s="0" t="s">
+      <c r="Q18" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="0" t="n">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="n">
         <v>27820</v>
       </c>
-      <c r="C19" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="0" t="s">
+      <c r="C19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="0" t="n">
+      <c r="F19" s="1" t="n">
         <v>8324075</v>
       </c>
-      <c r="G19" s="0" t="n">
+      <c r="G19" s="1" t="n">
         <v>4824892</v>
       </c>
-      <c r="H19" s="0" t="n">
+      <c r="H19" s="1" t="n">
         <v>3499184</v>
       </c>
-      <c r="I19" s="0" t="n">
+      <c r="I19" s="1" t="n">
         <v>1903774000</v>
       </c>
-      <c r="J19" s="0" t="n">
+      <c r="J19" s="1" t="n">
         <v>785088100</v>
       </c>
-      <c r="K19" s="0" t="n">
+      <c r="K19" s="1" t="n">
         <v>1117946000</v>
       </c>
-      <c r="L19" s="0" t="n">
+      <c r="L19" s="1" t="n">
         <v>82454140</v>
       </c>
-      <c r="M19" s="0" t="n">
+      <c r="M19" s="1" t="n">
         <v>54408710</v>
       </c>
-      <c r="N19" s="0" t="n">
+      <c r="N19" s="1" t="n">
         <v>136842100</v>
       </c>
-      <c r="O19" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P19" s="0" t="s">
+      <c r="O19" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P19" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="Q19" s="0" t="s">
+      <c r="Q19" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <v>27534</v>
       </c>
-      <c r="C20" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="0" t="s">
+      <c r="C20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F20" s="0" t="n">
+      <c r="F20" s="1" t="n">
         <v>8488004</v>
       </c>
-      <c r="G20" s="0" t="n">
+      <c r="G20" s="1" t="n">
         <v>5048184</v>
       </c>
-      <c r="H20" s="0" t="n">
+      <c r="H20" s="1" t="n">
         <v>3439820</v>
       </c>
-      <c r="I20" s="0" t="n">
+      <c r="I20" s="1" t="n">
         <v>2043546000</v>
       </c>
-      <c r="J20" s="0" t="n">
+      <c r="J20" s="1" t="n">
         <v>871771800</v>
       </c>
-      <c r="K20" s="0" t="n">
+      <c r="K20" s="1" t="n">
         <v>1171477000</v>
       </c>
-      <c r="L20" s="0" t="n">
+      <c r="L20" s="1" t="n">
         <v>86233270</v>
       </c>
-      <c r="M20" s="0" t="n">
+      <c r="M20" s="1" t="n">
         <v>53530230</v>
       </c>
-      <c r="N20" s="0" t="n">
+      <c r="N20" s="1" t="n">
         <v>139770200</v>
       </c>
-      <c r="O20" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P20" s="0" t="s">
+      <c r="O20" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P20" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="Q20" s="0" t="s">
+      <c r="Q20" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="1" t="n">
         <v>27250</v>
       </c>
-      <c r="C21" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="0" t="s">
+      <c r="C21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F21" s="0" t="n">
+      <c r="F21" s="1" t="n">
         <v>8744642</v>
       </c>
-      <c r="G21" s="0" t="n">
+      <c r="G21" s="1" t="n">
         <v>5330750</v>
       </c>
-      <c r="H21" s="0" t="n">
+      <c r="H21" s="1" t="n">
         <v>3413892</v>
       </c>
-      <c r="I21" s="0" t="n">
+      <c r="I21" s="1" t="n">
         <v>2187507000</v>
       </c>
-      <c r="J21" s="0" t="n">
+      <c r="J21" s="1" t="n">
         <v>962067300</v>
       </c>
-      <c r="K21" s="0" t="n">
+      <c r="K21" s="1" t="n">
         <v>1224408000</v>
       </c>
-      <c r="L21" s="0" t="n">
+      <c r="L21" s="1" t="n">
         <v>91036660</v>
       </c>
-      <c r="M21" s="0" t="n">
+      <c r="M21" s="1" t="n">
         <v>52929800</v>
       </c>
-      <c r="N21" s="0" t="n">
+      <c r="N21" s="1" t="n">
         <v>143961100</v>
       </c>
-      <c r="O21" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P21" s="0" t="s">
+      <c r="O21" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P21" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="Q21" s="0" t="s">
+      <c r="Q21" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="1" t="n">
         <v>26967</v>
       </c>
-      <c r="C22" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="0" t="s">
+      <c r="C22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="0" t="s">
+      <c r="E22" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="0" t="n">
+      <c r="F22" s="1" t="n">
         <v>8899755</v>
       </c>
-      <c r="G22" s="0" t="n">
+      <c r="G22" s="1" t="n">
         <v>5541254</v>
       </c>
-      <c r="H22" s="0" t="n">
+      <c r="H22" s="1" t="n">
         <v>3358500</v>
       </c>
-      <c r="I22" s="0" t="n">
+      <c r="I22" s="1" t="n">
         <v>2334246000</v>
       </c>
-      <c r="J22" s="0" t="n">
+      <c r="J22" s="1" t="n">
         <v>1056631000</v>
       </c>
-      <c r="K22" s="0" t="n">
+      <c r="K22" s="1" t="n">
         <v>1276478000</v>
       </c>
-      <c r="L22" s="0" t="n">
+      <c r="L22" s="1" t="n">
         <v>94644230</v>
       </c>
-      <c r="M22" s="0" t="n">
+      <c r="M22" s="1" t="n">
         <v>52067210</v>
       </c>
-      <c r="N22" s="0" t="n">
+      <c r="N22" s="1" t="n">
         <v>146738600</v>
       </c>
-      <c r="O22" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P22" s="0" t="s">
+      <c r="O22" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P22" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="Q22" s="0" t="s">
+      <c r="Q22" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="1" t="n">
         <v>26686</v>
       </c>
-      <c r="C23" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" s="0" t="s">
+      <c r="C23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="E23" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F23" s="0" t="n">
+      <c r="F23" s="1" t="n">
         <v>9049220</v>
       </c>
-      <c r="G23" s="0" t="n">
+      <c r="G23" s="1" t="n">
         <v>5747197</v>
       </c>
-      <c r="H23" s="0" t="n">
+      <c r="H23" s="1" t="n">
         <v>3302023</v>
       </c>
-      <c r="I23" s="0" t="n">
+      <c r="I23" s="1" t="n">
         <v>2483659000</v>
       </c>
-      <c r="J23" s="0" t="n">
+      <c r="J23" s="1" t="n">
         <v>1155340000</v>
       </c>
-      <c r="K23" s="0" t="n">
+      <c r="K23" s="1" t="n">
         <v>1327693000</v>
       </c>
-      <c r="L23" s="0" t="n">
+      <c r="L23" s="1" t="n">
         <v>98209270</v>
       </c>
-      <c r="M23" s="0" t="n">
+      <c r="M23" s="1" t="n">
         <v>51214070</v>
       </c>
-      <c r="N23" s="0" t="n">
+      <c r="N23" s="1" t="n">
         <v>149417800</v>
       </c>
-      <c r="O23" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P23" s="0" t="s">
+      <c r="O23" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P23" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="Q23" s="0" t="s">
+      <c r="Q23" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <v>26406</v>
       </c>
-      <c r="C24" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="0" t="s">
+      <c r="C24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F24" s="0" t="n">
+      <c r="F24" s="1" t="n">
         <v>9228751</v>
       </c>
-      <c r="G24" s="0" t="n">
+      <c r="G24" s="1" t="n">
         <v>5950560</v>
       </c>
-      <c r="H24" s="0" t="n">
+      <c r="H24" s="1" t="n">
         <v>3278191</v>
       </c>
-      <c r="I24" s="0" t="n">
+      <c r="I24" s="1" t="n">
         <v>2636230000</v>
       </c>
-      <c r="J24" s="0" t="n">
+      <c r="J24" s="1" t="n">
         <v>1256331000</v>
       </c>
-      <c r="K24" s="0" t="n">
+      <c r="K24" s="1" t="n">
         <v>1378613000</v>
       </c>
-      <c r="L24" s="0" t="n">
+      <c r="L24" s="1" t="n">
         <v>101640600</v>
       </c>
-      <c r="M24" s="0" t="n">
+      <c r="M24" s="1" t="n">
         <v>50922650</v>
       </c>
-      <c r="N24" s="0" t="n">
+      <c r="N24" s="1" t="n">
         <v>152551600</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <v>26117</v>
       </c>
-      <c r="C25" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="0" t="s">
+      <c r="C25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="0" t="s">
+      <c r="E25" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F25" s="0" t="n">
+      <c r="F25" s="1" t="n">
         <v>9366382</v>
       </c>
-      <c r="G25" s="0" t="n">
+      <c r="G25" s="1" t="n">
         <v>6142150</v>
       </c>
-      <c r="H25" s="0" t="n">
+      <c r="H25" s="1" t="n">
         <v>3224232</v>
       </c>
-      <c r="I25" s="0" t="n">
+      <c r="I25" s="1" t="n">
         <v>2791228000</v>
       </c>
-      <c r="J25" s="0" t="n">
+      <c r="J25" s="1" t="n">
         <v>1362966000</v>
       </c>
-      <c r="K25" s="0" t="n">
+      <c r="K25" s="1" t="n">
         <v>1428680000</v>
       </c>
-      <c r="L25" s="0" t="n">
+      <c r="L25" s="1" t="n">
         <v>104929000</v>
       </c>
-      <c r="M25" s="0" t="n">
+      <c r="M25" s="1" t="n">
         <v>50069650</v>
       </c>
-      <c r="N25" s="0" t="n">
+      <c r="N25" s="1" t="n">
         <v>155018300</v>
       </c>
-      <c r="O25" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P25" s="0" t="s">
+      <c r="O25" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P25" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="Q25" s="0" t="s">
+      <c r="Q25" s="1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="A26" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <v>25830</v>
       </c>
-      <c r="C26" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" s="0" t="s">
+      <c r="C26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E26" s="0" t="s">
+      <c r="E26" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F26" s="0" t="n">
+      <c r="F26" s="1" t="n">
         <v>9498485</v>
       </c>
-      <c r="G26" s="0" t="n">
+      <c r="G26" s="1" t="n">
         <v>6333458</v>
       </c>
-      <c r="H26" s="0" t="n">
+      <c r="H26" s="1" t="n">
         <v>3165027</v>
       </c>
-      <c r="I26" s="0" t="n">
+      <c r="I26" s="1" t="n">
         <v>2948621000</v>
       </c>
-      <c r="J26" s="0" t="n">
+      <c r="J26" s="1" t="n">
         <v>1471687000</v>
       </c>
-      <c r="K26" s="0" t="n">
+      <c r="K26" s="1" t="n">
         <v>1477906000</v>
       </c>
-      <c r="L26" s="0" t="n">
+      <c r="L26" s="1" t="n">
         <v>108146800</v>
       </c>
-      <c r="M26" s="0" t="n">
+      <c r="M26" s="1" t="n">
         <v>49226170</v>
       </c>
-      <c r="N26" s="0" t="n">
+      <c r="N26" s="1" t="n">
         <v>157390200</v>
       </c>
-      <c r="O26" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P26" s="0" t="s">
+      <c r="O26" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P26" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="Q26" s="0" t="s">
+      <c r="Q26" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+      <c r="A27" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="1" t="n">
         <v>25545</v>
       </c>
-      <c r="C27" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" s="0" t="s">
+      <c r="C27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E27" s="0" t="s">
+      <c r="E27" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F27" s="0" t="n">
+      <c r="F27" s="1" t="n">
         <v>9625249</v>
       </c>
-      <c r="G27" s="0" t="n">
+      <c r="G27" s="1" t="n">
         <v>6514992</v>
       </c>
-      <c r="H27" s="0" t="n">
+      <c r="H27" s="1" t="n">
         <v>3110258</v>
       </c>
-      <c r="I27" s="0" t="n">
+      <c r="I27" s="1" t="n">
         <v>3108303000</v>
       </c>
-      <c r="J27" s="0" t="n">
+      <c r="J27" s="1" t="n">
         <v>1582416000</v>
       </c>
-      <c r="K27" s="0" t="n">
+      <c r="K27" s="1" t="n">
         <v>1526297000</v>
       </c>
-      <c r="L27" s="0" t="n">
+      <c r="L27" s="1" t="n">
         <v>111297900</v>
       </c>
-      <c r="M27" s="0" t="n">
+      <c r="M27" s="1" t="n">
         <v>48392350</v>
       </c>
-      <c r="N27" s="0" t="n">
+      <c r="N27" s="1" t="n">
         <v>159668400</v>
       </c>
-      <c r="O27" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P27" s="0" t="s">
+      <c r="O27" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P27" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="Q27" s="0" t="s">
+      <c r="Q27" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+      <c r="A28" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="1" t="n">
         <v>25261</v>
       </c>
-      <c r="C28" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" s="0" t="s">
+      <c r="C28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E28" s="0" t="s">
+      <c r="E28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F28" s="0" t="n">
+      <c r="F28" s="1" t="n">
         <v>9746644</v>
       </c>
-      <c r="G28" s="0" t="n">
+      <c r="G28" s="1" t="n">
         <v>6689808</v>
       </c>
-      <c r="H28" s="0" t="n">
+      <c r="H28" s="1" t="n">
         <v>3056836</v>
       </c>
-      <c r="I28" s="0" t="n">
+      <c r="I28" s="1" t="n">
         <v>3270139000</v>
       </c>
-      <c r="J28" s="0" t="n">
+      <c r="J28" s="1" t="n">
         <v>1695080000</v>
       </c>
-      <c r="K28" s="0" t="n">
+      <c r="K28" s="1" t="n">
         <v>1573863000</v>
       </c>
-      <c r="L28" s="0" t="n">
+      <c r="L28" s="1" t="n">
         <v>114307700</v>
       </c>
-      <c r="M28" s="0" t="n">
+      <c r="M28" s="1" t="n">
         <v>47568130</v>
       </c>
-      <c r="N28" s="0" t="n">
+      <c r="N28" s="1" t="n">
         <v>161852700</v>
       </c>
-      <c r="O28" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P28" s="0" t="s">
+      <c r="O28" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P28" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="Q28" s="0" t="s">
+      <c r="Q28" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
+      <c r="A29" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="1" t="n">
         <v>24978</v>
       </c>
-      <c r="C29" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" s="0" t="s">
+      <c r="C29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E29" s="0" t="s">
+      <c r="E29" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F29" s="0" t="n">
+      <c r="F29" s="1" t="n">
         <v>9982158</v>
       </c>
-      <c r="G29" s="0" t="n">
+      <c r="G29" s="1" t="n">
         <v>6949174</v>
       </c>
-      <c r="H29" s="0" t="n">
+      <c r="H29" s="1" t="n">
         <v>3032983</v>
       </c>
-      <c r="I29" s="0" t="n">
+      <c r="I29" s="1" t="n">
         <v>3435830000</v>
       </c>
-      <c r="J29" s="0" t="n">
+      <c r="J29" s="1" t="n">
         <v>1814371000</v>
       </c>
-      <c r="K29" s="0" t="n">
+      <c r="K29" s="1" t="n">
         <v>1620874000</v>
       </c>
-      <c r="L29" s="0" t="n">
+      <c r="L29" s="1" t="n">
         <v>118670300</v>
       </c>
-      <c r="M29" s="0" t="n">
+      <c r="M29" s="1" t="n">
         <v>47005120</v>
       </c>
-      <c r="N29" s="0" t="n">
+      <c r="N29" s="1" t="n">
         <v>165685300</v>
       </c>
-      <c r="O29" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P29" s="0" t="s">
+      <c r="O29" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P29" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="Q29" s="0" t="s">
+      <c r="Q29" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
+      <c r="A30" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="1" t="n">
         <v>24698</v>
       </c>
-      <c r="C30" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="E30" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="F30" s="0" t="n">
+      <c r="C30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F30" s="1" t="n">
         <v>10095290</v>
       </c>
-      <c r="G30" s="0" t="n">
+      <c r="G30" s="1" t="n">
         <v>7114729</v>
       </c>
-      <c r="H30" s="0" t="n">
+      <c r="H30" s="1" t="n">
         <v>2980564</v>
       </c>
-      <c r="I30" s="0" t="n">
+      <c r="I30" s="1" t="n">
         <v>3603551000</v>
       </c>
-      <c r="J30" s="0" t="n">
+      <c r="J30" s="1" t="n">
         <v>1935438000</v>
       </c>
-      <c r="K30" s="0" t="n">
+      <c r="K30" s="1" t="n">
         <v>1667070000</v>
       </c>
-      <c r="L30" s="0" t="n">
+      <c r="L30" s="1" t="n">
         <v>121519600</v>
       </c>
-      <c r="M30" s="0" t="n">
+      <c r="M30" s="1" t="n">
         <v>46196760</v>
       </c>
-      <c r="N30" s="0" t="n">
+      <c r="N30" s="1" t="n">
         <v>167729100</v>
       </c>
-      <c r="O30" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P30" s="0" t="s">
+      <c r="O30" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P30" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="Q30" s="0" t="s">
+      <c r="Q30" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="n">
+      <c r="A31" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="1" t="n">
         <v>24419</v>
       </c>
-      <c r="C31" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" s="0" t="s">
+      <c r="C31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E31" s="0" t="s">
+      <c r="E31" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F31" s="0" t="n">
+      <c r="F31" s="1" t="n">
         <v>10203220</v>
       </c>
-      <c r="G31" s="0" t="n">
+      <c r="G31" s="1" t="n">
         <v>7274298</v>
       </c>
-      <c r="H31" s="0" t="n">
+      <c r="H31" s="1" t="n">
         <v>2928926</v>
       </c>
-      <c r="I31" s="0" t="n">
+      <c r="I31" s="1" t="n">
         <v>3773237000</v>
       </c>
-      <c r="J31" s="0" t="n">
+      <c r="J31" s="1" t="n">
         <v>2058208000</v>
       </c>
-      <c r="K31" s="0" t="n">
+      <c r="K31" s="1" t="n">
         <v>1712467000</v>
       </c>
-      <c r="L31" s="0" t="n">
+      <c r="L31" s="1" t="n">
         <v>124329700</v>
       </c>
-      <c r="M31" s="0" t="n">
+      <c r="M31" s="1" t="n">
         <v>45397790</v>
       </c>
-      <c r="N31" s="0" t="n">
+      <c r="N31" s="1" t="n">
         <v>169682600</v>
       </c>
-      <c r="O31" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P31" s="0" t="s">
+      <c r="O31" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P31" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="Q31" s="0" t="s">
+      <c r="Q31" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="n">
+      <c r="A32" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32" s="1" t="n">
         <v>24141</v>
       </c>
-      <c r="C32" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" s="0" t="s">
+      <c r="C32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E32" s="0" t="s">
+      <c r="E32" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F32" s="0" t="n">
+      <c r="F32" s="1" t="n">
         <v>10305930</v>
       </c>
-      <c r="G32" s="0" t="n">
+      <c r="G32" s="1" t="n">
         <v>7432021</v>
       </c>
-      <c r="H32" s="0" t="n">
+      <c r="H32" s="1" t="n">
         <v>2873907</v>
       </c>
-      <c r="I32" s="0" t="n">
+      <c r="I32" s="1" t="n">
         <v>3944787000</v>
       </c>
-      <c r="J32" s="0" t="n">
+      <c r="J32" s="1" t="n">
         <v>2185798000</v>
       </c>
-      <c r="K32" s="0" t="n">
+      <c r="K32" s="1" t="n">
         <v>1757076000</v>
       </c>
-      <c r="L32" s="0" t="n">
+      <c r="L32" s="1" t="n">
         <v>126952000</v>
       </c>
-      <c r="M32" s="0" t="n">
+      <c r="M32" s="1" t="n">
         <v>44608000</v>
       </c>
-      <c r="N32" s="0" t="n">
+      <c r="N32" s="1" t="n">
         <v>171545500</v>
       </c>
-      <c r="O32" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P32" s="0" t="s">
+      <c r="O32" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P32" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="Q32" s="0" t="s">
+      <c r="Q32" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="n">
+      <c r="A33" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="1" t="n">
         <v>23865</v>
       </c>
-      <c r="C33" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" s="0" t="s">
+      <c r="C33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E33" s="0" t="s">
+      <c r="E33" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F33" s="0" t="n">
+      <c r="F33" s="1" t="n">
         <v>10403570</v>
       </c>
-      <c r="G33" s="0" t="n">
+      <c r="G33" s="1" t="n">
         <v>7579937</v>
       </c>
-      <c r="H33" s="0" t="n">
+      <c r="H33" s="1" t="n">
         <v>2823635</v>
       </c>
-      <c r="I33" s="0" t="n">
+      <c r="I33" s="1" t="n">
         <v>4118106000</v>
       </c>
-      <c r="J33" s="0" t="n">
+      <c r="J33" s="1" t="n">
         <v>2317734000</v>
       </c>
-      <c r="K33" s="0" t="n">
+      <c r="K33" s="1" t="n">
         <v>1800902000</v>
       </c>
-      <c r="L33" s="0" t="n">
+      <c r="L33" s="1" t="n">
         <v>129502000</v>
       </c>
-      <c r="M33" s="0" t="n">
+      <c r="M33" s="1" t="n">
         <v>43827210</v>
       </c>
-      <c r="N33" s="0" t="n">
+      <c r="N33" s="1" t="n">
         <v>173319800</v>
       </c>
-      <c r="O33" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P33" s="0" t="s">
+      <c r="O33" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P33" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="Q33" s="0" t="s">
+      <c r="Q33" s="1" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="n">
+      <c r="A34" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="1" t="n">
         <v>23591</v>
       </c>
-      <c r="C34" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D34" s="0" t="s">
+      <c r="C34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E34" s="0" t="s">
+      <c r="E34" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F34" s="0" t="n">
+      <c r="F34" s="1" t="n">
         <v>10496150</v>
       </c>
-      <c r="G34" s="0" t="n">
+      <c r="G34" s="1" t="n">
         <v>7722613</v>
       </c>
-      <c r="H34" s="0" t="n">
+      <c r="H34" s="1" t="n">
         <v>2773538</v>
       </c>
-      <c r="I34" s="0" t="n">
+      <c r="I34" s="1" t="n">
         <v>4293122000</v>
       </c>
-      <c r="J34" s="0" t="n">
+      <c r="J34" s="1" t="n">
         <v>2448291000</v>
       </c>
-      <c r="K34" s="0" t="n">
+      <c r="K34" s="1" t="n">
         <v>1843955000</v>
       </c>
-      <c r="L34" s="0" t="n">
+      <c r="L34" s="1" t="n">
         <v>131927300</v>
       </c>
-      <c r="M34" s="0" t="n">
+      <c r="M34" s="1" t="n">
         <v>43055970</v>
       </c>
-      <c r="N34" s="0" t="n">
+      <c r="N34" s="1" t="n">
         <v>175006500</v>
       </c>
-      <c r="O34" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P34" s="0" t="s">
+      <c r="O34" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P34" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="Q34" s="0" t="s">
+      <c r="Q34" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="n">
+      <c r="A35" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B35" s="0" t="n">
+      <c r="B35" s="1" t="n">
         <v>23318</v>
       </c>
-      <c r="C35" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="0" t="s">
+      <c r="C35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="0" t="s">
+      <c r="E35" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F35" s="0" t="n">
+      <c r="F35" s="1" t="n">
         <v>10583760</v>
       </c>
-      <c r="G35" s="0" t="n">
+      <c r="G35" s="1" t="n">
         <v>7864646</v>
       </c>
-      <c r="H35" s="0" t="n">
+      <c r="H35" s="1" t="n">
         <v>2719115</v>
       </c>
-      <c r="I35" s="0" t="n">
+      <c r="I35" s="1" t="n">
         <v>4469737000</v>
       </c>
-      <c r="J35" s="0" t="n">
+      <c r="J35" s="1" t="n">
         <v>2583295000</v>
       </c>
-      <c r="K35" s="0" t="n">
+      <c r="K35" s="1" t="n">
         <v>1886250000</v>
       </c>
-      <c r="L35" s="0" t="n">
+      <c r="L35" s="1" t="n">
         <v>134282700</v>
       </c>
-      <c r="M35" s="0" t="n">
+      <c r="M35" s="1" t="n">
         <v>42293530</v>
       </c>
-      <c r="N35" s="0" t="n">
+      <c r="N35" s="1" t="n">
         <v>176606100</v>
       </c>
-      <c r="O35" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P35" s="0" t="s">
+      <c r="O35" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P35" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Q35" s="0" t="s">
+      <c r="Q35" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="n">
+      <c r="A36" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36" s="1" t="n">
         <v>23047</v>
       </c>
-      <c r="C36" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" s="0" t="s">
+      <c r="C36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E36" s="0" t="s">
+      <c r="E36" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F36" s="0" t="n">
+      <c r="F36" s="1" t="n">
         <v>10666420</v>
       </c>
-      <c r="G36" s="0" t="n">
+      <c r="G36" s="1" t="n">
         <v>7994173</v>
       </c>
-      <c r="H36" s="0" t="n">
+      <c r="H36" s="1" t="n">
         <v>2672248</v>
       </c>
-      <c r="I36" s="0" t="n">
+      <c r="I36" s="1" t="n">
         <v>4647853000</v>
       </c>
-      <c r="J36" s="0" t="n">
+      <c r="J36" s="1" t="n">
         <v>2722596000</v>
       </c>
-      <c r="K36" s="0" t="n">
+      <c r="K36" s="1" t="n">
         <v>1927790000</v>
       </c>
-      <c r="L36" s="0" t="n">
+      <c r="L36" s="1" t="n">
         <v>136606800</v>
       </c>
-      <c r="M36" s="0" t="n">
+      <c r="M36" s="1" t="n">
         <v>41540460</v>
       </c>
-      <c r="N36" s="0" t="n">
+      <c r="N36" s="1" t="n">
         <v>178120500</v>
       </c>
-      <c r="O36" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P36" s="0" t="s">
+      <c r="O36" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P36" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="Q36" s="0" t="s">
+      <c r="Q36" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="n">
+      <c r="A37" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B37" s="0" t="n">
+      <c r="B37" s="1" t="n">
         <v>22777</v>
       </c>
-      <c r="C37" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" s="0" t="s">
+      <c r="C37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E37" s="0" t="s">
+      <c r="E37" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F37" s="0" t="n">
+      <c r="F37" s="1" t="n">
         <v>10744200</v>
       </c>
-      <c r="G37" s="0" t="n">
+      <c r="G37" s="1" t="n">
         <v>8120090</v>
       </c>
-      <c r="H37" s="0" t="n">
+      <c r="H37" s="1" t="n">
         <v>2624112</v>
       </c>
-      <c r="I37" s="0" t="n">
+      <c r="I37" s="1" t="n">
         <v>4827305000</v>
       </c>
-      <c r="J37" s="0" t="n">
+      <c r="J37" s="1" t="n">
         <v>2860071000</v>
       </c>
-      <c r="K37" s="0" t="n">
+      <c r="K37" s="1" t="n">
         <v>1968585000</v>
       </c>
-      <c r="L37" s="0" t="n">
+      <c r="L37" s="1" t="n">
         <v>138771200</v>
       </c>
-      <c r="M37" s="0" t="n">
+      <c r="M37" s="1" t="n">
         <v>40796320</v>
       </c>
-      <c r="N37" s="0" t="n">
+      <c r="N37" s="1" t="n">
         <v>179549400</v>
       </c>
-      <c r="O37" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P37" s="0" t="s">
+      <c r="O37" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P37" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="Q37" s="0" t="s">
+      <c r="Q37" s="1" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="n">
+      <c r="A38" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B38" s="0" t="n">
+      <c r="B38" s="1" t="n">
         <v>22509</v>
       </c>
-      <c r="C38" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D38" s="0" t="s">
+      <c r="C38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E38" s="0" t="s">
+      <c r="E38" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F38" s="0" t="n">
+      <c r="F38" s="1" t="n">
         <v>10956740</v>
       </c>
-      <c r="G38" s="0" t="n">
+      <c r="G38" s="1" t="n">
         <v>8355994</v>
       </c>
-      <c r="H38" s="0" t="n">
+      <c r="H38" s="1" t="n">
         <v>2600747</v>
       </c>
-      <c r="I38" s="0" t="n">
+      <c r="I38" s="1" t="n">
         <v>5010386000</v>
       </c>
-      <c r="J38" s="0" t="n">
+      <c r="J38" s="1" t="n">
         <v>3003522000</v>
       </c>
-      <c r="K38" s="0" t="n">
+      <c r="K38" s="1" t="n">
         <v>2008877000</v>
       </c>
-      <c r="L38" s="0" t="n">
+      <c r="L38" s="1" t="n">
         <v>142706500</v>
       </c>
-      <c r="M38" s="0" t="n">
+      <c r="M38" s="1" t="n">
         <v>40288740</v>
       </c>
-      <c r="N38" s="0" t="n">
+      <c r="N38" s="1" t="n">
         <v>183005900</v>
       </c>
-      <c r="O38" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P38" s="0" t="s">
+      <c r="O38" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P38" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="Q38" s="0" t="s">
+      <c r="Q38" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="n">
+      <c r="A39" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B39" s="0" t="n">
+      <c r="B39" s="1" t="n">
         <v>22243</v>
       </c>
-      <c r="C39" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D39" s="0" t="s">
+      <c r="C39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E39" s="0" t="s">
+      <c r="E39" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F39" s="0" t="n">
+      <c r="F39" s="1" t="n">
         <v>11026830</v>
       </c>
-      <c r="G39" s="0" t="n">
+      <c r="G39" s="1" t="n">
         <v>8472014</v>
       </c>
-      <c r="H39" s="0" t="n">
+      <c r="H39" s="1" t="n">
         <v>2554811</v>
       </c>
-      <c r="I39" s="0" t="n">
+      <c r="I39" s="1" t="n">
         <v>5194717000</v>
       </c>
-      <c r="J39" s="0" t="n">
+      <c r="J39" s="1" t="n">
         <v>3150978000</v>
       </c>
-      <c r="K39" s="0" t="n">
+      <c r="K39" s="1" t="n">
         <v>2048434000</v>
       </c>
-      <c r="L39" s="0" t="n">
+      <c r="L39" s="1" t="n">
         <v>144733800</v>
       </c>
-      <c r="M39" s="0" t="n">
+      <c r="M39" s="1" t="n">
         <v>39559950</v>
       </c>
-      <c r="N39" s="0" t="n">
+      <c r="N39" s="1" t="n">
         <v>184305600</v>
       </c>
-      <c r="O39" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P39" s="0" t="s">
+      <c r="O39" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P39" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="Q39" s="0" t="s">
+      <c r="Q39" s="1" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="n">
+      <c r="A40" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B40" s="0" t="n">
+      <c r="B40" s="1" t="n">
         <v>21978</v>
       </c>
-      <c r="C40" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D40" s="0" t="s">
+      <c r="C40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E40" s="0" t="s">
+      <c r="E40" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="F40" s="0" t="n">
+      <c r="F40" s="1" t="n">
         <v>11092180</v>
       </c>
-      <c r="G40" s="0" t="n">
+      <c r="G40" s="1" t="n">
         <v>8589115</v>
       </c>
-      <c r="H40" s="0" t="n">
+      <c r="H40" s="1" t="n">
         <v>2503067</v>
       </c>
-      <c r="I40" s="0" t="n">
+      <c r="I40" s="1" t="n">
         <v>5380153000</v>
       </c>
-      <c r="J40" s="0" t="n">
+      <c r="J40" s="1" t="n">
         <v>3296475000</v>
       </c>
-      <c r="K40" s="0" t="n">
+      <c r="K40" s="1" t="n">
         <v>2087266000</v>
       </c>
-      <c r="L40" s="0" t="n">
+      <c r="L40" s="1" t="n">
         <v>146715600</v>
       </c>
-      <c r="M40" s="0" t="n">
+      <c r="M40" s="1" t="n">
         <v>38839770</v>
       </c>
-      <c r="N40" s="0" t="n">
+      <c r="N40" s="1" t="n">
         <v>185521300</v>
       </c>
-      <c r="O40" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P40" s="0" t="s">
+      <c r="O40" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P40" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="Q40" s="0" t="s">
+      <c r="Q40" s="1" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="n">
-        <v>17</v>
-      </c>
-      <c r="B41" s="0" t="n">
+      <c r="A41" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B41" s="1" t="n">
         <v>21715</v>
       </c>
-      <c r="C41" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D41" s="0" t="s">
+      <c r="C41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E41" s="0" t="s">
+      <c r="E41" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F41" s="0" t="n">
+      <c r="F41" s="1" t="n">
         <v>11152920</v>
       </c>
-      <c r="G41" s="0" t="n">
+      <c r="G41" s="1" t="n">
         <v>8695733</v>
       </c>
-      <c r="H41" s="0" t="n">
+      <c r="H41" s="1" t="n">
         <v>2457186</v>
       </c>
-      <c r="I41" s="0" t="n">
+      <c r="I41" s="1" t="n">
         <v>5566828000</v>
       </c>
-      <c r="J41" s="0" t="n">
+      <c r="J41" s="1" t="n">
         <v>3445767000</v>
       </c>
-      <c r="K41" s="0" t="n">
+      <c r="K41" s="1" t="n">
         <v>2125393000</v>
       </c>
-      <c r="L41" s="0" t="n">
+      <c r="L41" s="1" t="n">
         <v>148543100</v>
       </c>
-      <c r="M41" s="0" t="n">
+      <c r="M41" s="1" t="n">
         <v>38128500</v>
       </c>
-      <c r="N41" s="0" t="n">
+      <c r="N41" s="1" t="n">
         <v>186656300</v>
       </c>
-      <c r="O41" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P41" s="0" t="s">
+      <c r="O41" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P41" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="Q41" s="0" t="s">
+      <c r="Q41" s="1" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="n">
+      <c r="A42" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B42" s="0" t="n">
+      <c r="B42" s="1" t="n">
         <v>21453</v>
       </c>
-      <c r="C42" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D42" s="0" t="s">
+      <c r="C42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E42" s="0" t="s">
+      <c r="E42" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="F42" s="0" t="n">
+      <c r="F42" s="1" t="n">
         <v>11209040</v>
       </c>
-      <c r="G42" s="0" t="n">
+      <c r="G42" s="1" t="n">
         <v>8796797</v>
       </c>
-      <c r="H42" s="0" t="n">
+      <c r="H42" s="1" t="n">
         <v>2412238</v>
       </c>
-      <c r="I42" s="0" t="n">
+      <c r="I42" s="1" t="n">
         <v>5754581000</v>
       </c>
-      <c r="J42" s="0" t="n">
+      <c r="J42" s="1" t="n">
         <v>3598713000</v>
       </c>
-      <c r="K42" s="0" t="n">
+      <c r="K42" s="1" t="n">
         <v>2162813000</v>
       </c>
-      <c r="L42" s="0" t="n">
+      <c r="L42" s="1" t="n">
         <v>150275100</v>
       </c>
-      <c r="M42" s="0" t="n">
+      <c r="M42" s="1" t="n">
         <v>37426080</v>
       </c>
-      <c r="N42" s="0" t="n">
+      <c r="N42" s="1" t="n">
         <v>187710600</v>
       </c>
-      <c r="O42" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P42" s="0" t="s">
+      <c r="O42" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P42" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="Q42" s="0" t="s">
+      <c r="Q42" s="1" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="n">
+      <c r="A43" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" s="1" t="n">
         <v>21193</v>
       </c>
-      <c r="C43" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D43" s="0" t="s">
+      <c r="C43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E43" s="0" t="s">
+      <c r="E43" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F43" s="0" t="n">
+      <c r="F43" s="1" t="n">
         <v>11332030</v>
       </c>
-      <c r="G43" s="0" t="n">
+      <c r="G43" s="1" t="n">
         <v>8896465</v>
       </c>
-      <c r="H43" s="0" t="n">
+      <c r="H43" s="1" t="n">
         <v>2435565</v>
       </c>
-      <c r="I43" s="0" t="n">
+      <c r="I43" s="1" t="n">
         <v>8428053000</v>
       </c>
-      <c r="J43" s="0" t="n">
+      <c r="J43" s="1" t="n">
         <v>4910513000</v>
       </c>
-      <c r="K43" s="0" t="n">
+      <c r="K43" s="1" t="n">
         <v>3528351000</v>
       </c>
-      <c r="L43" s="0" t="n">
+      <c r="L43" s="1" t="n">
         <v>151929200</v>
       </c>
-      <c r="M43" s="0" t="n">
+      <c r="M43" s="1" t="n">
         <v>37841420</v>
       </c>
-      <c r="N43" s="0" t="n">
+      <c r="N43" s="1" t="n">
         <v>189794800</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="n">
+      <c r="A44" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B44" s="0" t="n">
+      <c r="B44" s="1" t="n">
         <v>20934</v>
       </c>
-      <c r="C44" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D44" s="0" t="s">
+      <c r="C44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E44" s="0" t="s">
+      <c r="E44" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F44" s="0" t="n">
+      <c r="F44" s="1" t="n">
         <v>11378410</v>
       </c>
-      <c r="G44" s="0" t="n">
+      <c r="G44" s="1" t="n">
         <v>8987477</v>
       </c>
-      <c r="H44" s="0" t="n">
+      <c r="H44" s="1" t="n">
         <v>2390937</v>
       </c>
-      <c r="I44" s="0" t="n">
+      <c r="I44" s="1" t="n">
         <v>8618692000</v>
       </c>
-      <c r="J44" s="0" t="n">
+      <c r="J44" s="1" t="n">
         <v>5064837000</v>
       </c>
-      <c r="K44" s="0" t="n">
+      <c r="K44" s="1" t="n">
         <v>3565507000</v>
       </c>
-      <c r="L44" s="0" t="n">
+      <c r="L44" s="1" t="n">
         <v>153517600</v>
       </c>
-      <c r="M44" s="0" t="n">
+      <c r="M44" s="1" t="n">
         <v>37146630</v>
       </c>
-      <c r="N44" s="0" t="n">
+      <c r="N44" s="1" t="n">
         <v>190681300</v>
       </c>
-      <c r="O44" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P44" s="0" t="s">
+      <c r="O44" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P44" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="Q44" s="0" t="s">
+      <c r="Q44" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="n">
+      <c r="A45" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B45" s="0" t="n">
+      <c r="B45" s="1" t="n">
         <v>20677</v>
       </c>
-      <c r="C45" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D45" s="0" t="s">
+      <c r="C45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E45" s="0" t="s">
+      <c r="E45" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F45" s="0" t="n">
+      <c r="F45" s="1" t="n">
         <v>11420260</v>
       </c>
-      <c r="G45" s="0" t="n">
+      <c r="G45" s="1" t="n">
         <v>9074699</v>
       </c>
-      <c r="H45" s="0" t="n">
+      <c r="H45" s="1" t="n">
         <v>2345563</v>
       </c>
-      <c r="I45" s="0" t="n">
+      <c r="I45" s="1" t="n">
         <v>8810357000</v>
       </c>
-      <c r="J45" s="0" t="n">
+      <c r="J45" s="1" t="n">
         <v>5217040000</v>
       </c>
-      <c r="K45" s="0" t="n">
+      <c r="K45" s="1" t="n">
         <v>3601978000</v>
       </c>
-      <c r="L45" s="0" t="n">
+      <c r="L45" s="1" t="n">
         <v>155040800</v>
       </c>
-      <c r="M45" s="0" t="n">
+      <c r="M45" s="1" t="n">
         <v>36460610</v>
       </c>
-      <c r="N45" s="0" t="n">
+      <c r="N45" s="1" t="n">
         <v>191489700</v>
       </c>
-      <c r="O45" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P45" s="0" t="s">
+      <c r="O45" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P45" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="Q45" s="0" t="s">
+      <c r="Q45" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="n">
+      <c r="A46" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B46" s="0" t="n">
+      <c r="B46" s="1" t="n">
         <v>20421</v>
       </c>
-      <c r="C46" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D46" s="0" t="s">
+      <c r="C46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E46" s="0" t="s">
+      <c r="E46" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F46" s="0" t="n">
+      <c r="F46" s="1" t="n">
         <v>11457720</v>
       </c>
-      <c r="G46" s="0" t="n">
+      <c r="G46" s="1" t="n">
         <v>9159359</v>
       </c>
-      <c r="H46" s="0" t="n">
+      <c r="H46" s="1" t="n">
         <v>2298359</v>
       </c>
-      <c r="I46" s="0" t="n">
+      <c r="I46" s="1" t="n">
         <v>9002864000</v>
       </c>
-      <c r="J46" s="0" t="n">
+      <c r="J46" s="1" t="n">
         <v>5377857000</v>
       </c>
-      <c r="K46" s="0" t="n">
+      <c r="K46" s="1" t="n">
         <v>3637769000</v>
       </c>
-      <c r="L46" s="0" t="n">
+      <c r="L46" s="1" t="n">
         <v>156455100</v>
       </c>
-      <c r="M46" s="0" t="n">
+      <c r="M46" s="1" t="n">
         <v>35783160</v>
       </c>
-      <c r="N46" s="0" t="n">
+      <c r="N46" s="1" t="n">
         <v>192222500</v>
       </c>
-      <c r="O46" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P46" s="0" t="s">
+      <c r="O46" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P46" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="Q46" s="0" t="s">
+      <c r="Q46" s="1" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="n">
+      <c r="A47" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B47" s="0" t="n">
+      <c r="B47" s="1" t="n">
         <v>20167</v>
       </c>
-      <c r="C47" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D47" s="0" t="s">
+      <c r="C47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E47" s="0" t="s">
+      <c r="E47" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="F47" s="0" t="n">
+      <c r="F47" s="1" t="n">
         <v>11649070</v>
       </c>
-      <c r="G47" s="0" t="n">
+      <c r="G47" s="1" t="n">
         <v>9365671</v>
       </c>
-      <c r="H47" s="0" t="n">
+      <c r="H47" s="1" t="n">
         <v>2283401</v>
       </c>
-      <c r="I47" s="0" t="n">
+      <c r="I47" s="1" t="n">
         <v>9198154000</v>
       </c>
-      <c r="J47" s="0" t="n">
+      <c r="J47" s="1" t="n">
         <v>5538675000</v>
       </c>
-      <c r="K47" s="0" t="n">
+      <c r="K47" s="1" t="n">
         <v>3673112000</v>
       </c>
-      <c r="L47" s="0" t="n">
+      <c r="L47" s="1" t="n">
         <v>160005300</v>
       </c>
-      <c r="M47" s="0" t="n">
+      <c r="M47" s="1" t="n">
         <v>35329040</v>
       </c>
-      <c r="N47" s="0" t="n">
+      <c r="N47" s="1" t="n">
         <v>195324100</v>
       </c>
-      <c r="O47" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P47" s="0" t="s">
+      <c r="O47" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P47" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="Q47" s="0" t="s">
+      <c r="Q47" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="n">
+      <c r="A48" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B48" s="0" t="n">
+      <c r="B48" s="1" t="n">
         <v>19914</v>
       </c>
-      <c r="C48" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D48" s="0" t="s">
+      <c r="C48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E48" s="0" t="s">
+      <c r="E48" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F48" s="0" t="n">
+      <c r="F48" s="1" t="n">
         <v>11679410</v>
       </c>
-      <c r="G48" s="0" t="n">
+      <c r="G48" s="1" t="n">
         <v>9438860</v>
       </c>
-      <c r="H48" s="0" t="n">
+      <c r="H48" s="1" t="n">
         <v>2240550</v>
       </c>
-      <c r="I48" s="0" t="n">
+      <c r="I48" s="1" t="n">
         <v>9393704000</v>
       </c>
-      <c r="J48" s="0" t="n">
+      <c r="J48" s="1" t="n">
         <v>5697251000</v>
       </c>
-      <c r="K48" s="0" t="n">
+      <c r="K48" s="1" t="n">
         <v>3707778000</v>
       </c>
-      <c r="L48" s="0" t="n">
+      <c r="L48" s="1" t="n">
         <v>161246000</v>
       </c>
-      <c r="M48" s="0" t="n">
+      <c r="M48" s="1" t="n">
         <v>34666090</v>
       </c>
-      <c r="N48" s="0" t="n">
+      <c r="N48" s="1" t="n">
         <v>195936300</v>
       </c>
-      <c r="O48" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P48" s="0" t="s">
+      <c r="O48" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P48" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="Q48" s="0" t="s">
+      <c r="Q48" s="1" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="n">
+      <c r="A49" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B49" s="0" t="n">
+      <c r="B49" s="1" t="n">
         <v>19664</v>
       </c>
-      <c r="C49" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D49" s="0" t="s">
+      <c r="C49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E49" s="0" t="s">
+      <c r="E49" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F49" s="0" t="n">
+      <c r="F49" s="1" t="n">
         <v>11705650</v>
       </c>
-      <c r="G49" s="0" t="n">
+      <c r="G49" s="1" t="n">
         <v>9511337</v>
       </c>
-      <c r="H49" s="0" t="n">
+      <c r="H49" s="1" t="n">
         <v>2194317</v>
       </c>
-      <c r="I49" s="0" t="n">
+      <c r="I49" s="1" t="n">
         <v>9589759000</v>
       </c>
-      <c r="J49" s="0" t="n">
+      <c r="J49" s="1" t="n">
         <v>5864025000</v>
       </c>
-      <c r="K49" s="0" t="n">
+      <c r="K49" s="1" t="n">
         <v>3741785000</v>
       </c>
-      <c r="L49" s="0" t="n">
+      <c r="L49" s="1" t="n">
         <v>162505400</v>
       </c>
-      <c r="M49" s="0" t="n">
+      <c r="M49" s="1" t="n">
         <v>34011240</v>
       </c>
-      <c r="N49" s="0" t="n">
+      <c r="N49" s="1" t="n">
         <v>196474300</v>
       </c>
-      <c r="O49" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P49" s="0" t="s">
+      <c r="O49" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P49" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="Q49" s="0" t="s">
+      <c r="Q49" s="1" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="n">
+      <c r="A50" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B50" s="0" t="n">
+      <c r="B50" s="1" t="n">
         <v>19414</v>
       </c>
-      <c r="C50" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D50" s="0" t="s">
+      <c r="C50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E50" s="0" t="s">
+      <c r="E50" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F50" s="0" t="n">
+      <c r="F50" s="1" t="n">
         <v>11727630</v>
       </c>
-      <c r="G50" s="0" t="n">
+      <c r="G50" s="1" t="n">
         <v>9575947</v>
       </c>
-      <c r="H50" s="0" t="n">
+      <c r="H50" s="1" t="n">
         <v>2151688</v>
       </c>
-      <c r="I50" s="0" t="n">
+      <c r="I50" s="1" t="n">
         <v>9786716000</v>
       </c>
-      <c r="J50" s="0" t="n">
+      <c r="J50" s="1" t="n">
         <v>6028441000</v>
       </c>
-      <c r="K50" s="0" t="n">
+      <c r="K50" s="1" t="n">
         <v>3775145000</v>
       </c>
-      <c r="L50" s="0" t="n">
+      <c r="L50" s="1" t="n">
         <v>163579800</v>
       </c>
-      <c r="M50" s="0" t="n">
+      <c r="M50" s="1" t="n">
         <v>33364710</v>
       </c>
-      <c r="N50" s="0" t="n">
+      <c r="N50" s="1" t="n">
         <v>196939900</v>
       </c>
-      <c r="O50" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P50" s="0" t="s">
+      <c r="O50" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P50" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="Q50" s="0" t="s">
+      <c r="Q50" s="1" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="n">
+      <c r="A51" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B51" s="0" t="n">
+      <c r="B51" s="1" t="n">
         <v>19167</v>
       </c>
-      <c r="C51" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D51" s="0" t="s">
+      <c r="C51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E51" s="0" t="s">
+      <c r="E51" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="F51" s="0" t="n">
+      <c r="F51" s="1" t="n">
         <v>11745450</v>
       </c>
-      <c r="G51" s="0" t="n">
+      <c r="G51" s="1" t="n">
         <v>9634861</v>
       </c>
-      <c r="H51" s="0" t="n">
+      <c r="H51" s="1" t="n">
         <v>2110587</v>
       </c>
-      <c r="I51" s="0" t="n">
+      <c r="I51" s="1" t="n">
         <v>9984317000</v>
       </c>
-      <c r="J51" s="0" t="n">
+      <c r="J51" s="1" t="n">
         <v>6190518000</v>
       </c>
-      <c r="K51" s="0" t="n">
+      <c r="K51" s="1" t="n">
         <v>3807858000</v>
       </c>
-      <c r="L51" s="0" t="n">
+      <c r="L51" s="1" t="n">
         <v>164608600</v>
       </c>
-      <c r="M51" s="0" t="n">
+      <c r="M51" s="1" t="n">
         <v>32726680</v>
       </c>
-      <c r="N51" s="0" t="n">
+      <c r="N51" s="1" t="n">
         <v>197333000</v>
       </c>
-      <c r="O51" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P51" s="0" t="s">
+      <c r="O51" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P51" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="Q51" s="0" t="s">
+      <c r="Q51" s="1" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="n">
+      <c r="A52" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B52" s="0" t="n">
+      <c r="B52" s="1" t="n">
         <v>18921</v>
       </c>
-      <c r="C52" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D52" s="0" t="s">
+      <c r="C52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E52" s="0" t="s">
+      <c r="E52" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F52" s="0" t="n">
+      <c r="F52" s="1" t="n">
         <v>11759180</v>
       </c>
-      <c r="G52" s="0" t="n">
+      <c r="G52" s="1" t="n">
         <v>9692979</v>
       </c>
-      <c r="H52" s="0" t="n">
+      <c r="H52" s="1" t="n">
         <v>2066203</v>
       </c>
-      <c r="I52" s="0" t="n">
+      <c r="I52" s="1" t="n">
         <v>10182270000</v>
       </c>
-      <c r="J52" s="0" t="n">
+      <c r="J52" s="1" t="n">
         <v>6360255000</v>
       </c>
-      <c r="K52" s="0" t="n">
+      <c r="K52" s="1" t="n">
         <v>3839935000</v>
       </c>
-      <c r="L52" s="0" t="n">
+      <c r="L52" s="1" t="n">
         <v>165559100</v>
       </c>
-      <c r="M52" s="0" t="n">
+      <c r="M52" s="1" t="n">
         <v>32097030</v>
       </c>
-      <c r="N52" s="0" t="n">
+      <c r="N52" s="1" t="n">
         <v>197653800</v>
       </c>
-      <c r="O52" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P52" s="0" t="s">
+      <c r="O52" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P52" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="Q52" s="0" t="s">
+      <c r="Q52" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="n">
+      <c r="A53" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B53" s="0" t="n">
+      <c r="B53" s="1" t="n">
         <v>18676</v>
       </c>
-      <c r="C53" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D53" s="0" t="s">
+      <c r="C53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E53" s="0" t="s">
+      <c r="E53" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F53" s="0" t="n">
+      <c r="F53" s="1" t="n">
         <v>11768860</v>
       </c>
-      <c r="G53" s="0" t="n">
+      <c r="G53" s="1" t="n">
         <v>9741521</v>
       </c>
-      <c r="H53" s="0" t="n">
+      <c r="H53" s="1" t="n">
         <v>2027342</v>
       </c>
-      <c r="I53" s="0" t="n">
+      <c r="I53" s="1" t="n">
         <v>10380360000</v>
       </c>
-      <c r="J53" s="0" t="n">
+      <c r="J53" s="1" t="n">
         <v>6527541000</v>
       </c>
-      <c r="K53" s="0" t="n">
+      <c r="K53" s="1" t="n">
         <v>3871393000</v>
       </c>
-      <c r="L53" s="0" t="n">
+      <c r="L53" s="1" t="n">
         <v>166393900</v>
       </c>
-      <c r="M53" s="0" t="n">
+      <c r="M53" s="1" t="n">
         <v>31475440</v>
       </c>
-      <c r="N53" s="0" t="n">
+      <c r="N53" s="1" t="n">
         <v>197905400</v>
       </c>
-      <c r="O53" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P53" s="0" t="s">
+      <c r="O53" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P53" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="Q53" s="0" t="s">
+      <c r="Q53" s="1" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="n">
+      <c r="A54" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B54" s="0" t="n">
+      <c r="B54" s="1" t="n">
         <v>18433</v>
       </c>
-      <c r="C54" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D54" s="0" t="s">
+      <c r="C54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E54" s="0" t="s">
+      <c r="E54" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="F54" s="0" t="n">
+      <c r="F54" s="1" t="n">
         <v>11774650</v>
       </c>
-      <c r="G54" s="0" t="n">
+      <c r="G54" s="1" t="n">
         <v>9790351</v>
       </c>
-      <c r="H54" s="0" t="n">
+      <c r="H54" s="1" t="n">
         <v>1984301</v>
       </c>
-      <c r="I54" s="0" t="n">
+      <c r="I54" s="1" t="n">
         <v>10578320000</v>
       </c>
-      <c r="J54" s="0" t="n">
+      <c r="J54" s="1" t="n">
         <v>6692394000</v>
       </c>
-      <c r="K54" s="0" t="n">
+      <c r="K54" s="1" t="n">
         <v>3902243000</v>
       </c>
-      <c r="L54" s="0" t="n">
+      <c r="L54" s="1" t="n">
         <v>167252000</v>
       </c>
-      <c r="M54" s="0" t="n">
+      <c r="M54" s="1" t="n">
         <v>30861760</v>
       </c>
-      <c r="N54" s="0" t="n">
+      <c r="N54" s="1" t="n">
         <v>198087300</v>
       </c>
-      <c r="O54" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P54" s="0" t="s">
+      <c r="O54" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P54" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="Q54" s="0" t="s">
+      <c r="Q54" s="1" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="n">
+      <c r="A55" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B55" s="0" t="n">
+      <c r="B55" s="1" t="n">
         <v>18192</v>
       </c>
-      <c r="C55" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D55" s="0" t="s">
+      <c r="C55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E55" s="0" t="s">
+      <c r="E55" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F55" s="0" t="n">
+      <c r="F55" s="1" t="n">
         <v>11776450</v>
       </c>
-      <c r="G55" s="0" t="n">
+      <c r="G55" s="1" t="n">
         <v>9830934</v>
       </c>
-      <c r="H55" s="0" t="n">
+      <c r="H55" s="1" t="n">
         <v>1945519</v>
       </c>
-      <c r="I55" s="0" t="n">
+      <c r="I55" s="1" t="n">
         <v>10776150000</v>
       </c>
-      <c r="J55" s="0" t="n">
+      <c r="J55" s="1" t="n">
         <v>6864387000</v>
       </c>
-      <c r="K55" s="0" t="n">
+      <c r="K55" s="1" t="n">
         <v>3932489000</v>
       </c>
-      <c r="L55" s="0" t="n">
+      <c r="L55" s="1" t="n">
         <v>167932600</v>
       </c>
-      <c r="M55" s="0" t="n">
+      <c r="M55" s="1" t="n">
         <v>30256530</v>
       </c>
-      <c r="N55" s="0" t="n">
+      <c r="N55" s="1" t="n">
         <v>198200600</v>
       </c>
-      <c r="O55" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P55" s="0" t="s">
+      <c r="O55" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P55" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="Q55" s="0" t="s">
+      <c r="Q55" s="1" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="n">
+      <c r="A56" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B56" s="0" t="n">
+      <c r="B56" s="1" t="n">
         <v>17952</v>
       </c>
-      <c r="C56" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D56" s="0" t="s">
+      <c r="C56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E56" s="0" t="s">
+      <c r="E56" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F56" s="0" t="n">
+      <c r="F56" s="1" t="n">
         <v>11774330</v>
       </c>
-      <c r="G56" s="0" t="n">
+      <c r="G56" s="1" t="n">
         <v>9869599</v>
       </c>
-      <c r="H56" s="0" t="n">
+      <c r="H56" s="1" t="n">
         <v>1904736</v>
       </c>
-      <c r="I56" s="0" t="n">
+      <c r="I56" s="1" t="n">
         <v>10974150000</v>
       </c>
-      <c r="J56" s="0" t="n">
+      <c r="J56" s="1" t="n">
         <v>7033841000</v>
       </c>
-      <c r="K56" s="0" t="n">
+      <c r="K56" s="1" t="n">
         <v>3962139000</v>
       </c>
-      <c r="L56" s="0" t="n">
+      <c r="L56" s="1" t="n">
         <v>168573300</v>
       </c>
-      <c r="M56" s="0" t="n">
+      <c r="M56" s="1" t="n">
         <v>29659030</v>
       </c>
-      <c r="N56" s="0" t="n">
+      <c r="N56" s="1" t="n">
         <v>198245400</v>
       </c>
-      <c r="O56" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P56" s="0" t="s">
+      <c r="O56" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P56" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="Q56" s="0" t="s">
+      <c r="Q56" s="1" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="n">
+      <c r="A57" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B57" s="0" t="n">
+      <c r="B57" s="1" t="n">
         <v>17714</v>
       </c>
-      <c r="C57" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D57" s="0" t="s">
+      <c r="C57" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E57" s="0" t="s">
+      <c r="E57" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="F57" s="0" t="n">
+      <c r="F57" s="1" t="n">
         <v>11942370</v>
       </c>
-      <c r="G57" s="0" t="n">
+      <c r="G57" s="1" t="n">
         <v>10053600</v>
       </c>
-      <c r="H57" s="0" t="n">
+      <c r="H57" s="1" t="n">
         <v>1888771</v>
       </c>
-      <c r="I57" s="0" t="n">
+      <c r="I57" s="1" t="n">
         <v>11175200000</v>
       </c>
-      <c r="J57" s="0" t="n">
+      <c r="J57" s="1" t="n">
         <v>7203295000</v>
       </c>
-      <c r="K57" s="0" t="n">
+      <c r="K57" s="1" t="n">
         <v>3991389000</v>
       </c>
-      <c r="L57" s="0" t="n">
+      <c r="L57" s="1" t="n">
         <v>171713300</v>
       </c>
-      <c r="M57" s="0" t="n">
+      <c r="M57" s="1" t="n">
         <v>29260200</v>
       </c>
-      <c r="N57" s="0" t="n">
+      <c r="N57" s="1" t="n">
         <v>200968800</v>
       </c>
-      <c r="O57" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P57" s="0" t="s">
+      <c r="O57" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P57" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="Q57" s="0" t="s">
+      <c r="Q57" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="n">
+      <c r="A58" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B58" s="0" t="n">
+      <c r="B58" s="1" t="n">
         <v>17477</v>
       </c>
-      <c r="C58" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D58" s="0" t="s">
+      <c r="C58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E58" s="0" t="s">
+      <c r="E58" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F58" s="0" t="n">
+      <c r="F58" s="1" t="n">
         <v>11934020</v>
       </c>
-      <c r="G58" s="0" t="n">
+      <c r="G58" s="1" t="n">
         <v>10082710</v>
       </c>
-      <c r="H58" s="0" t="n">
+      <c r="H58" s="1" t="n">
         <v>1851308</v>
       </c>
-      <c r="I58" s="0" t="n">
+      <c r="I58" s="1" t="n">
         <v>11376340000</v>
       </c>
-      <c r="J58" s="0" t="n">
+      <c r="J58" s="1" t="n">
         <v>7379503000</v>
       </c>
-      <c r="K58" s="0" t="n">
+      <c r="K58" s="1" t="n">
         <v>4020058000</v>
       </c>
-      <c r="L58" s="0" t="n">
+      <c r="L58" s="1" t="n">
         <v>172238200</v>
       </c>
-      <c r="M58" s="0" t="n">
+      <c r="M58" s="1" t="n">
         <v>28676250</v>
       </c>
-      <c r="N58" s="0" t="n">
+      <c r="N58" s="1" t="n">
         <v>200907700</v>
       </c>
-      <c r="O58" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P58" s="0" t="s">
+      <c r="O58" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P58" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="Q58" s="0" t="s">
+      <c r="Q58" s="1" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="n">
+      <c r="A59" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B59" s="0" t="n">
+      <c r="B59" s="1" t="n">
         <v>17242</v>
       </c>
-      <c r="C59" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D59" s="0" t="s">
+      <c r="C59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E59" s="0" t="s">
+      <c r="E59" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="F59" s="0" t="n">
+      <c r="F59" s="1" t="n">
         <v>11921860</v>
       </c>
-      <c r="G59" s="0" t="n">
+      <c r="G59" s="1" t="n">
         <v>10107360</v>
       </c>
-      <c r="H59" s="0" t="n">
+      <c r="H59" s="1" t="n">
         <v>1814500</v>
       </c>
-      <c r="I59" s="0" t="n">
+      <c r="I59" s="1" t="n">
         <v>11577370000</v>
       </c>
-      <c r="J59" s="0" t="n">
+      <c r="J59" s="1" t="n">
         <v>7553072000</v>
       </c>
-      <c r="K59" s="0" t="n">
+      <c r="K59" s="1" t="n">
         <v>4048155000</v>
       </c>
-      <c r="L59" s="0" t="n">
+      <c r="L59" s="1" t="n">
         <v>172705300</v>
       </c>
-      <c r="M59" s="0" t="n">
+      <c r="M59" s="1" t="n">
         <v>28100380</v>
       </c>
-      <c r="N59" s="0" t="n">
+      <c r="N59" s="1" t="n">
         <v>200780600</v>
       </c>
-      <c r="O59" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P59" s="0" t="s">
+      <c r="O59" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P59" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="Q59" s="0" t="s">
+      <c r="Q59" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="n">
+      <c r="A60" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B60" s="0" t="n">
+      <c r="B60" s="1" t="n">
         <v>17009</v>
       </c>
-      <c r="C60" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D60" s="0" t="s">
+      <c r="C60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E60" s="0" t="s">
+      <c r="E60" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F60" s="0" t="n">
+      <c r="F60" s="1" t="n">
         <v>11986830</v>
       </c>
-      <c r="G60" s="0" t="n">
+      <c r="G60" s="1" t="n">
         <v>10130680</v>
       </c>
-      <c r="H60" s="0" t="n">
+      <c r="H60" s="1" t="n">
         <v>1856155</v>
       </c>
-      <c r="I60" s="0" t="n">
+      <c r="I60" s="1" t="n">
         <v>20017020000</v>
       </c>
-      <c r="J60" s="0" t="n">
+      <c r="J60" s="1" t="n">
         <v>12487070000</v>
       </c>
-      <c r="K60" s="0" t="n">
+      <c r="K60" s="1" t="n">
         <v>7567463000</v>
       </c>
-      <c r="L60" s="0" t="n">
+      <c r="L60" s="1" t="n">
         <v>173086500</v>
       </c>
-      <c r="M60" s="0" t="n">
+      <c r="M60" s="1" t="n">
         <v>28782200</v>
       </c>
-      <c r="N60" s="0" t="n">
+      <c r="N60" s="1" t="n">
         <v>201840100</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="n">
+      <c r="A61" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B61" s="0" t="n">
+      <c r="B61" s="1" t="n">
         <v>16774</v>
       </c>
-      <c r="C61" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D61" s="0" t="s">
+      <c r="C61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E61" s="0" t="s">
+      <c r="E61" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="F61" s="0" t="n">
+      <c r="F61" s="1" t="n">
         <v>11966430</v>
       </c>
-      <c r="G61" s="0" t="n">
+      <c r="G61" s="1" t="n">
         <v>10149940</v>
       </c>
-      <c r="H61" s="0" t="n">
+      <c r="H61" s="1" t="n">
         <v>1816490</v>
       </c>
-      <c r="I61" s="0" t="n">
+      <c r="I61" s="1" t="n">
         <v>20219180000</v>
       </c>
-      <c r="J61" s="0" t="n">
+      <c r="J61" s="1" t="n">
         <v>12664280000</v>
       </c>
-      <c r="K61" s="0" t="n">
+      <c r="K61" s="1" t="n">
         <v>7595696000</v>
       </c>
-      <c r="L61" s="0" t="n">
+      <c r="L61" s="1" t="n">
         <v>173339700</v>
       </c>
-      <c r="M61" s="0" t="n">
+      <c r="M61" s="1" t="n">
         <v>28205580</v>
       </c>
-      <c r="N61" s="0" t="n">
+      <c r="N61" s="1" t="n">
         <v>201569500</v>
       </c>
-      <c r="O61" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P61" s="0" t="s">
+      <c r="O61" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P61" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="Q61" s="0" t="s">
+      <c r="Q61" s="1" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="n">
+      <c r="A62" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B62" s="0" t="n">
+      <c r="B62" s="1" t="n">
         <v>16540</v>
       </c>
-      <c r="C62" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D62" s="0" t="s">
+      <c r="C62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E62" s="0" t="s">
+      <c r="E62" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F62" s="0" t="n">
+      <c r="F62" s="1" t="n">
         <v>11942550</v>
       </c>
-      <c r="G62" s="0" t="n">
+      <c r="G62" s="1" t="n">
         <v>10162400</v>
       </c>
-      <c r="H62" s="0" t="n">
+      <c r="H62" s="1" t="n">
         <v>1780156</v>
       </c>
-      <c r="I62" s="0" t="n">
+      <c r="I62" s="1" t="n">
         <v>20421660000</v>
       </c>
-      <c r="J62" s="0" t="n">
+      <c r="J62" s="1" t="n">
         <v>12838770000</v>
       </c>
-      <c r="K62" s="0" t="n">
+      <c r="K62" s="1" t="n">
         <v>7623360000</v>
       </c>
-      <c r="L62" s="0" t="n">
+      <c r="L62" s="1" t="n">
         <v>173594200</v>
       </c>
-      <c r="M62" s="0" t="n">
+      <c r="M62" s="1" t="n">
         <v>27636700</v>
       </c>
-      <c r="N62" s="0" t="n">
+      <c r="N62" s="1" t="n">
         <v>201236900</v>
       </c>
-      <c r="O62" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P62" s="0" t="s">
+      <c r="O62" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P62" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="Q62" s="0" t="s">
+      <c r="Q62" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="n">
+      <c r="A63" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B63" s="0" t="n">
+      <c r="B63" s="1" t="n">
         <v>16308</v>
       </c>
-      <c r="C63" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D63" s="0" t="s">
+      <c r="C63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E63" s="0" t="s">
+      <c r="E63" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="F63" s="0" t="n">
+      <c r="F63" s="1" t="n">
         <v>11915090</v>
       </c>
-      <c r="G63" s="0" t="n">
+      <c r="G63" s="1" t="n">
         <v>10173200</v>
       </c>
-      <c r="H63" s="0" t="n">
+      <c r="H63" s="1" t="n">
         <v>1741892</v>
       </c>
-      <c r="I63" s="0" t="n">
+      <c r="I63" s="1" t="n">
         <v>20623930000</v>
       </c>
-      <c r="J63" s="0" t="n">
+      <c r="J63" s="1" t="n">
         <v>13010570000</v>
       </c>
-      <c r="K63" s="0" t="n">
+      <c r="K63" s="1" t="n">
         <v>7650466000</v>
       </c>
-      <c r="L63" s="0" t="n">
+      <c r="L63" s="1" t="n">
         <v>173762700</v>
       </c>
-      <c r="M63" s="0" t="n">
+      <c r="M63" s="1" t="n">
         <v>27075540</v>
       </c>
-      <c r="N63" s="0" t="n">
+      <c r="N63" s="1" t="n">
         <v>200843800</v>
       </c>
-      <c r="O63" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P63" s="0" t="s">
+      <c r="O63" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P63" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="Q63" s="0" t="s">
+      <c r="Q63" s="1" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="n">
+      <c r="A64" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B64" s="0" t="n">
+      <c r="B64" s="1" t="n">
         <v>16077</v>
       </c>
-      <c r="C64" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D64" s="0" t="s">
+      <c r="C64" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E64" s="0" t="s">
+      <c r="E64" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F64" s="0" t="n">
+      <c r="F64" s="1" t="n">
         <v>11884250</v>
       </c>
-      <c r="G64" s="0" t="n">
+      <c r="G64" s="1" t="n">
         <v>10177500</v>
       </c>
-      <c r="H64" s="0" t="n">
+      <c r="H64" s="1" t="n">
         <v>1706747</v>
       </c>
-      <c r="I64" s="0" t="n">
+      <c r="I64" s="1" t="n">
         <v>20825520000</v>
       </c>
-      <c r="J64" s="0" t="n">
+      <c r="J64" s="1" t="n">
         <v>13179700000</v>
       </c>
-      <c r="K64" s="0" t="n">
+      <c r="K64" s="1" t="n">
         <v>7677025000</v>
       </c>
-      <c r="L64" s="0" t="n">
+      <c r="L64" s="1" t="n">
         <v>173879900</v>
       </c>
-      <c r="M64" s="0" t="n">
+      <c r="M64" s="1" t="n">
         <v>26522270</v>
       </c>
-      <c r="N64" s="0" t="n">
+      <c r="N64" s="1" t="n">
         <v>200389500</v>
       </c>
-      <c r="O64" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P64" s="0" t="s">
+      <c r="O64" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P64" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="Q64" s="0" t="s">
+      <c r="Q64" s="1" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="n">
+      <c r="A65" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B65" s="0" t="n">
+      <c r="B65" s="1" t="n">
         <v>15849</v>
       </c>
-      <c r="C65" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D65" s="0" t="s">
+      <c r="C65" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E65" s="0" t="s">
+      <c r="E65" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F65" s="0" t="n">
+      <c r="F65" s="1" t="n">
         <v>11849980</v>
       </c>
-      <c r="G65" s="0" t="n">
+      <c r="G65" s="1" t="n">
         <v>10178130</v>
       </c>
-      <c r="H65" s="0" t="n">
+      <c r="H65" s="1" t="n">
         <v>1671845</v>
       </c>
-      <c r="I65" s="0" t="n">
+      <c r="I65" s="1" t="n">
         <v>21025770000</v>
       </c>
-      <c r="J65" s="0" t="n">
+      <c r="J65" s="1" t="n">
         <v>13346170000</v>
       </c>
-      <c r="K65" s="0" t="n">
+      <c r="K65" s="1" t="n">
         <v>7703051000</v>
       </c>
-      <c r="L65" s="0" t="n">
+      <c r="L65" s="1" t="n">
         <v>173914000</v>
       </c>
-      <c r="M65" s="0" t="n">
+      <c r="M65" s="1" t="n">
         <v>25976600</v>
       </c>
-      <c r="N65" s="0" t="n">
+      <c r="N65" s="1" t="n">
         <v>199876400</v>
       </c>
-      <c r="O65" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P65" s="0" t="s">
+      <c r="O65" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P65" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="Q65" s="0" t="s">
+      <c r="Q65" s="1" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="n">
+      <c r="A66" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B66" s="0" t="n">
+      <c r="B66" s="1" t="n">
         <v>15621</v>
       </c>
-      <c r="C66" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D66" s="0" t="s">
+      <c r="C66" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E66" s="0" t="s">
+      <c r="E66" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F66" s="0" t="n">
+      <c r="F66" s="1" t="n">
         <v>11812400</v>
       </c>
-      <c r="G66" s="0" t="n">
+      <c r="G66" s="1" t="n">
         <v>10177990</v>
       </c>
-      <c r="H66" s="0" t="n">
+      <c r="H66" s="1" t="n">
         <v>1634415</v>
       </c>
-      <c r="I66" s="0" t="n">
+      <c r="I66" s="1" t="n">
         <v>21224530000</v>
       </c>
-      <c r="J66" s="0" t="n">
+      <c r="J66" s="1" t="n">
         <v>13526390000</v>
       </c>
-      <c r="K66" s="0" t="n">
+      <c r="K66" s="1" t="n">
         <v>7728532000</v>
       </c>
-      <c r="L66" s="0" t="n">
+      <c r="L66" s="1" t="n">
         <v>173844500</v>
       </c>
-      <c r="M66" s="0" t="n">
+      <c r="M66" s="1" t="n">
         <v>25438660</v>
       </c>
-      <c r="N66" s="0" t="n">
+      <c r="N66" s="1" t="n">
         <v>199306200</v>
       </c>
-      <c r="O66" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P66" s="0" t="s">
+      <c r="O66" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P66" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="Q66" s="0" t="s">
+      <c r="Q66" s="1" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="n">
+      <c r="A67" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B67" s="0" t="n">
+      <c r="B67" s="1" t="n">
         <v>15396</v>
       </c>
-      <c r="C67" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D67" s="0" t="s">
+      <c r="C67" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E67" s="0" t="s">
+      <c r="E67" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="F67" s="0" t="n">
+      <c r="F67" s="1" t="n">
         <v>11959290</v>
       </c>
-      <c r="G67" s="0" t="n">
+      <c r="G67" s="1" t="n">
         <v>10337730</v>
       </c>
-      <c r="H67" s="0" t="n">
+      <c r="H67" s="1" t="n">
         <v>1621564</v>
       </c>
-      <c r="I67" s="0" t="n">
+      <c r="I67" s="1" t="n">
         <v>21425510000</v>
       </c>
-      <c r="J67" s="0" t="n">
+      <c r="J67" s="1" t="n">
         <v>13706620000</v>
       </c>
-      <c r="K67" s="0" t="n">
+      <c r="K67" s="1" t="n">
         <v>7753665000</v>
       </c>
-      <c r="L67" s="0" t="n">
+      <c r="L67" s="1" t="n">
         <v>176616300</v>
       </c>
-      <c r="M67" s="0" t="n">
+      <c r="M67" s="1" t="n">
         <v>25087070</v>
       </c>
-      <c r="N67" s="0" t="n">
+      <c r="N67" s="1" t="n">
         <v>201671500</v>
       </c>
-      <c r="O67" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P67" s="0" t="s">
+      <c r="O67" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P67" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="Q67" s="0" t="s">
+      <c r="Q67" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="n">
+      <c r="A68" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B68" s="0" t="n">
+      <c r="B68" s="1" t="n">
         <v>15172</v>
       </c>
-      <c r="C68" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D68" s="0" t="s">
+      <c r="C68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E68" s="0" t="s">
+      <c r="E68" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F68" s="0" t="n">
+      <c r="F68" s="1" t="n">
         <v>11916010</v>
       </c>
-      <c r="G68" s="0" t="n">
+      <c r="G68" s="1" t="n">
         <v>10331120</v>
       </c>
-      <c r="H68" s="0" t="n">
+      <c r="H68" s="1" t="n">
         <v>1584896</v>
       </c>
-      <c r="I68" s="0" t="n">
+      <c r="I68" s="1" t="n">
         <v>21625580000</v>
       </c>
-      <c r="J68" s="0" t="n">
+      <c r="J68" s="1" t="n">
         <v>13883970000</v>
       </c>
-      <c r="K68" s="0" t="n">
+      <c r="K68" s="1" t="n">
         <v>7778281000</v>
       </c>
-      <c r="L68" s="0" t="n">
+      <c r="L68" s="1" t="n">
         <v>176436500</v>
       </c>
-      <c r="M68" s="0" t="n">
+      <c r="M68" s="1" t="n">
         <v>24561860</v>
       </c>
-      <c r="N68" s="0" t="n">
+      <c r="N68" s="1" t="n">
         <v>201005900</v>
       </c>
-      <c r="O68" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P68" s="0" t="s">
+      <c r="O68" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P68" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="Q68" s="0" t="s">
+      <c r="Q68" s="1" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="n">
+      <c r="A69" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B69" s="0" t="n">
+      <c r="B69" s="1" t="n">
         <v>14950</v>
       </c>
-      <c r="C69" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D69" s="0" t="s">
+      <c r="C69" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E69" s="0" t="s">
+      <c r="E69" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F69" s="0" t="n">
+      <c r="F69" s="1" t="n">
         <v>11869690</v>
       </c>
-      <c r="G69" s="0" t="n">
+      <c r="G69" s="1" t="n">
         <v>10317880</v>
       </c>
-      <c r="H69" s="0" t="n">
+      <c r="H69" s="1" t="n">
         <v>1551808</v>
       </c>
-      <c r="I69" s="0" t="n">
+      <c r="I69" s="1" t="n">
         <v>21824810000</v>
       </c>
-      <c r="J69" s="0" t="n">
+      <c r="J69" s="1" t="n">
         <v>14058470000</v>
       </c>
-      <c r="K69" s="0" t="n">
+      <c r="K69" s="1" t="n">
         <v>7802372000</v>
       </c>
-      <c r="L69" s="0" t="n">
+      <c r="L69" s="1" t="n">
         <v>176238200</v>
       </c>
-      <c r="M69" s="0" t="n">
+      <c r="M69" s="1" t="n">
         <v>24043930</v>
       </c>
-      <c r="N69" s="0" t="n">
+      <c r="N69" s="1" t="n">
         <v>200284400</v>
       </c>
-      <c r="O69" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P69" s="0" t="s">
+      <c r="O69" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P69" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="Q69" s="0" t="s">
+      <c r="Q69" s="1" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="n">
+      <c r="A70" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B70" s="0" t="n">
+      <c r="B70" s="1" t="n">
         <v>14729</v>
       </c>
-      <c r="C70" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D70" s="0" t="s">
+      <c r="C70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E70" s="0" t="s">
+      <c r="E70" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="F70" s="0" t="n">
+      <c r="F70" s="1" t="n">
         <v>11820200</v>
       </c>
-      <c r="G70" s="0" t="n">
+      <c r="G70" s="1" t="n">
         <v>10300110</v>
       </c>
-      <c r="H70" s="0" t="n">
+      <c r="H70" s="1" t="n">
         <v>1520089</v>
       </c>
-      <c r="I70" s="0" t="n">
+      <c r="I70" s="1" t="n">
         <v>22023210000</v>
       </c>
-      <c r="J70" s="0" t="n">
+      <c r="J70" s="1" t="n">
         <v>14230150000</v>
       </c>
-      <c r="K70" s="0" t="n">
+      <c r="K70" s="1" t="n">
         <v>7825946000</v>
       </c>
-      <c r="L70" s="0" t="n">
+      <c r="L70" s="1" t="n">
         <v>175977200</v>
       </c>
-      <c r="M70" s="0" t="n">
+      <c r="M70" s="1" t="n">
         <v>23533620</v>
       </c>
-      <c r="N70" s="0" t="n">
+      <c r="N70" s="1" t="n">
         <v>199508000</v>
       </c>
-      <c r="O70" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P70" s="0" t="s">
+      <c r="O70" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P70" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="Q70" s="0" t="s">
+      <c r="Q70" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="n">
+      <c r="A71" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B71" s="0" t="n">
+      <c r="B71" s="1" t="n">
         <v>14510</v>
       </c>
-      <c r="C71" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D71" s="0" t="s">
+      <c r="C71" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E71" s="0" t="s">
+      <c r="E71" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F71" s="0" t="n">
+      <c r="F71" s="1" t="n">
         <v>11767570</v>
       </c>
-      <c r="G71" s="0" t="n">
+      <c r="G71" s="1" t="n">
         <v>10282550</v>
       </c>
-      <c r="H71" s="0" t="n">
+      <c r="H71" s="1" t="n">
         <v>1485023</v>
       </c>
-      <c r="I71" s="0" t="n">
+      <c r="I71" s="1" t="n">
         <v>22220950000</v>
       </c>
-      <c r="J71" s="0" t="n">
+      <c r="J71" s="1" t="n">
         <v>14399020000</v>
       </c>
-      <c r="K71" s="0" t="n">
+      <c r="K71" s="1" t="n">
         <v>7849002000</v>
       </c>
-      <c r="L71" s="0" t="n">
+      <c r="L71" s="1" t="n">
         <v>175614000</v>
       </c>
-      <c r="M71" s="0" t="n">
+      <c r="M71" s="1" t="n">
         <v>23030550</v>
       </c>
-      <c r="N71" s="0" t="n">
+      <c r="N71" s="1" t="n">
         <v>198677800</v>
       </c>
-      <c r="O71" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P71" s="0" t="s">
+      <c r="O71" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P71" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="Q71" s="0" t="s">
+      <c r="Q71" s="1" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="n">
+      <c r="A72" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B72" s="0" t="n">
+      <c r="B72" s="1" t="n">
         <v>14293</v>
       </c>
-      <c r="C72" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D72" s="0" t="s">
+      <c r="C72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E72" s="0" t="s">
+      <c r="E72" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F72" s="0" t="n">
+      <c r="F72" s="1" t="n">
         <v>11711930</v>
       </c>
-      <c r="G72" s="0" t="n">
+      <c r="G72" s="1" t="n">
         <v>10258670</v>
       </c>
-      <c r="H72" s="0" t="n">
+      <c r="H72" s="1" t="n">
         <v>1453259</v>
       </c>
-      <c r="I72" s="0" t="n">
+      <c r="I72" s="1" t="n">
         <v>22418190000</v>
       </c>
-      <c r="J72" s="0" t="n">
+      <c r="J72" s="1" t="n">
         <v>14580220000</v>
       </c>
-      <c r="K72" s="0" t="n">
+      <c r="K72" s="1" t="n">
         <v>7871546000</v>
       </c>
-      <c r="L72" s="0" t="n">
+      <c r="L72" s="1" t="n">
         <v>175278000</v>
       </c>
-      <c r="M72" s="0" t="n">
+      <c r="M72" s="1" t="n">
         <v>22534850</v>
       </c>
-      <c r="N72" s="0" t="n">
+      <c r="N72" s="1" t="n">
         <v>197794100</v>
       </c>
-      <c r="O72" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P72" s="0" t="s">
+      <c r="O72" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P72" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="Q72" s="0" t="s">
+      <c r="Q72" s="1" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="n">
+      <c r="A73" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B73" s="0" t="n">
+      <c r="B73" s="1" t="n">
         <v>14077</v>
       </c>
-      <c r="C73" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D73" s="0" t="s">
+      <c r="C73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E73" s="0" t="s">
+      <c r="E73" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F73" s="0" t="n">
+      <c r="F73" s="1" t="n">
         <v>11653340</v>
       </c>
-      <c r="G73" s="0" t="n">
+      <c r="G73" s="1" t="n">
         <v>10233750</v>
       </c>
-      <c r="H73" s="0" t="n">
+      <c r="H73" s="1" t="n">
         <v>1419587</v>
       </c>
-      <c r="I73" s="0" t="n">
+      <c r="I73" s="1" t="n">
         <v>22615440000</v>
       </c>
-      <c r="J73" s="0" t="n">
+      <c r="J73" s="1" t="n">
         <v>14758400000</v>
       </c>
-      <c r="K73" s="0" t="n">
+      <c r="K73" s="1" t="n">
         <v>7893587000</v>
       </c>
-      <c r="L73" s="0" t="n">
+      <c r="L73" s="1" t="n">
         <v>174796500</v>
       </c>
-      <c r="M73" s="0" t="n">
+      <c r="M73" s="1" t="n">
         <v>22046470</v>
       </c>
-      <c r="N73" s="0" t="n">
+      <c r="N73" s="1" t="n">
         <v>196859100</v>
       </c>
-      <c r="O73" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P73" s="0" t="s">
+      <c r="O73" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P73" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="Q73" s="0" t="s">
+      <c r="Q73" s="1" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="n">
+      <c r="A74" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B74" s="0" t="n">
+      <c r="B74" s="1" t="n">
         <v>13863</v>
       </c>
-      <c r="C74" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D74" s="0" t="s">
+      <c r="C74" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="E74" s="0" t="s">
+      <c r="E74" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="F74" s="0" t="n">
+      <c r="F74" s="1" t="n">
         <v>11591840</v>
       </c>
-      <c r="G74" s="0" t="n">
+      <c r="G74" s="1" t="n">
         <v>10205150</v>
       </c>
-      <c r="H74" s="0" t="n">
+      <c r="H74" s="1" t="n">
         <v>1386692</v>
       </c>
-      <c r="I74" s="0" t="n">
+      <c r="I74" s="1" t="n">
         <v>22812820000</v>
       </c>
-      <c r="J74" s="0" t="n">
+      <c r="J74" s="1" t="n">
         <v>14933610000</v>
       </c>
-      <c r="K74" s="0" t="n">
+      <c r="K74" s="1" t="n">
         <v>7915122000</v>
       </c>
-      <c r="L74" s="0" t="n">
+      <c r="L74" s="1" t="n">
         <v>174296200</v>
       </c>
-      <c r="M74" s="0" t="n">
+      <c r="M74" s="1" t="n">
         <v>21565190</v>
       </c>
-      <c r="N74" s="0" t="n">
+      <c r="N74" s="1" t="n">
         <v>195872700</v>
       </c>
-      <c r="O74" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P74" s="0" t="s">
+      <c r="O74" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P74" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="Q74" s="0" t="s">
+      <c r="Q74" s="1" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="n">
+      <c r="A75" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B75" s="0" t="n">
+      <c r="B75" s="1" t="n">
         <v>13651</v>
       </c>
-      <c r="C75" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D75" s="0" t="s">
+      <c r="C75" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="E75" s="0" t="s">
+      <c r="E75" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="F75" s="0" t="n">
+      <c r="F75" s="1" t="n">
         <v>11601740</v>
       </c>
-      <c r="G75" s="0" t="n">
+      <c r="G75" s="1" t="n">
         <v>10170930</v>
       </c>
-      <c r="H75" s="0" t="n">
+      <c r="H75" s="1" t="n">
         <v>1430804</v>
       </c>
-      <c r="I75" s="0" t="n">
+      <c r="I75" s="1" t="n">
         <v>42816240000</v>
       </c>
-      <c r="J75" s="0" t="n">
+      <c r="J75" s="1" t="n">
         <v>27412980000</v>
       </c>
-      <c r="K75" s="0" t="n">
+      <c r="K75" s="1" t="n">
         <v>15475350000</v>
       </c>
-      <c r="L75" s="0" t="n">
+      <c r="L75" s="1" t="n">
         <v>173746700</v>
       </c>
-      <c r="M75" s="0" t="n">
+      <c r="M75" s="1" t="n">
         <v>22245250</v>
       </c>
-      <c r="N75" s="0" t="n">
+      <c r="N75" s="1" t="n">
         <v>195991200</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="n">
+      <c r="A76" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B76" s="0" t="n">
+      <c r="B76" s="1" t="n">
         <v>13449</v>
       </c>
-      <c r="C76" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D76" s="0" t="s">
+      <c r="C76" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E76" s="0" t="s">
+      <c r="E76" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F76" s="0" t="n">
+      <c r="F76" s="1" t="n">
         <v>11533930</v>
       </c>
-      <c r="G76" s="0" t="n">
+      <c r="G76" s="1" t="n">
         <v>10133670</v>
       </c>
-      <c r="H76" s="0" t="n">
+      <c r="H76" s="1" t="n">
         <v>1400257</v>
       </c>
-      <c r="I76" s="0" t="n">
+      <c r="I76" s="1" t="n">
         <v>43005720000</v>
       </c>
-      <c r="J76" s="0" t="n">
+      <c r="J76" s="1" t="n">
         <v>27582290000</v>
       </c>
-      <c r="K76" s="0" t="n">
+      <c r="K76" s="1" t="n">
         <v>15496460000</v>
       </c>
-      <c r="L76" s="0" t="n">
+      <c r="L76" s="1" t="n">
         <v>173130300</v>
       </c>
-      <c r="M76" s="0" t="n">
+      <c r="M76" s="1" t="n">
         <v>21774070</v>
       </c>
-      <c r="N76" s="0" t="n">
+      <c r="N76" s="1" t="n">
         <v>194901600</v>
       </c>
-      <c r="O76" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P76" s="0" t="s">
+      <c r="O76" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P76" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="Q76" s="0" t="s">
+      <c r="Q76" s="1" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="n">
+      <c r="A77" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B77" s="0" t="n">
+      <c r="B77" s="1" t="n">
         <v>13248</v>
       </c>
-      <c r="C77" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D77" s="0" t="s">
+      <c r="C77" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E77" s="0" t="s">
+      <c r="E77" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="F77" s="0" t="n">
+      <c r="F77" s="1" t="n">
         <v>11661270</v>
       </c>
-      <c r="G77" s="0" t="n">
+      <c r="G77" s="1" t="n">
         <v>10271390</v>
       </c>
-      <c r="H77" s="0" t="n">
+      <c r="H77" s="1" t="n">
         <v>1389876</v>
       </c>
-      <c r="I77" s="0" t="n">
+      <c r="I77" s="1" t="n">
         <v>43199980000</v>
       </c>
-      <c r="J77" s="0" t="n">
+      <c r="J77" s="1" t="n">
         <v>27751610000</v>
       </c>
-      <c r="K77" s="0" t="n">
+      <c r="K77" s="1" t="n">
         <v>15517320000</v>
       </c>
-      <c r="L77" s="0" t="n">
+      <c r="L77" s="1" t="n">
         <v>175483600</v>
       </c>
-      <c r="M77" s="0" t="n">
+      <c r="M77" s="1" t="n">
         <v>21478130</v>
       </c>
-      <c r="N77" s="0" t="n">
+      <c r="N77" s="1" t="n">
         <v>196946300</v>
       </c>
-      <c r="O77" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P77" s="0" t="s">
+      <c r="O77" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P77" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="Q77" s="0" t="s">
+      <c r="Q77" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="n">
+      <c r="A78" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B78" s="0" t="n">
+      <c r="B78" s="1" t="n">
         <v>13049</v>
       </c>
-      <c r="C78" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D78" s="0" t="s">
+      <c r="C78" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="E78" s="0" t="s">
+      <c r="E78" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="F78" s="0" t="n">
+      <c r="F78" s="1" t="n">
         <v>11588430</v>
       </c>
-      <c r="G78" s="0" t="n">
+      <c r="G78" s="1" t="n">
         <v>10230810</v>
       </c>
-      <c r="H78" s="0" t="n">
+      <c r="H78" s="1" t="n">
         <v>1357620</v>
       </c>
-      <c r="I78" s="0" t="n">
+      <c r="I78" s="1" t="n">
         <v>43396610000</v>
       </c>
-      <c r="J78" s="0" t="n">
+      <c r="J78" s="1" t="n">
         <v>27918020000</v>
       </c>
-      <c r="K78" s="0" t="n">
+      <c r="K78" s="1" t="n">
         <v>15537770000</v>
       </c>
-      <c r="L78" s="0" t="n">
+      <c r="L78" s="1" t="n">
         <v>174774500</v>
       </c>
-      <c r="M78" s="0" t="n">
+      <c r="M78" s="1" t="n">
         <v>21018370</v>
       </c>
-      <c r="N78" s="0" t="n">
+      <c r="N78" s="1" t="n">
         <v>195773400</v>
       </c>
-      <c r="O78" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P78" s="0" t="s">
+      <c r="O78" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P78" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="Q78" s="0" t="s">
+      <c r="Q78" s="1" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="n">
+      <c r="A79" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B79" s="0" t="n">
+      <c r="B79" s="1" t="n">
         <v>12851</v>
       </c>
-      <c r="C79" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D79" s="0" t="s">
+      <c r="C79" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E79" s="0" t="s">
+      <c r="E79" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="F79" s="0" t="n">
+      <c r="F79" s="1" t="n">
         <v>11513010</v>
       </c>
-      <c r="G79" s="0" t="n">
+      <c r="G79" s="1" t="n">
         <v>10184830</v>
       </c>
-      <c r="H79" s="0" t="n">
+      <c r="H79" s="1" t="n">
         <v>1328181</v>
       </c>
-      <c r="I79" s="0" t="n">
+      <c r="I79" s="1" t="n">
         <v>43596980000</v>
       </c>
-      <c r="J79" s="0" t="n">
+      <c r="J79" s="1" t="n">
         <v>28081550000</v>
       </c>
-      <c r="K79" s="0" t="n">
+      <c r="K79" s="1" t="n">
         <v>15557830000</v>
       </c>
-      <c r="L79" s="0" t="n">
+      <c r="L79" s="1" t="n">
         <v>173976700</v>
       </c>
-      <c r="M79" s="0" t="n">
+      <c r="M79" s="1" t="n">
         <v>20565130</v>
       </c>
-      <c r="N79" s="0" t="n">
+      <c r="N79" s="1" t="n">
         <v>194554300</v>
       </c>
-      <c r="O79" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P79" s="0" t="s">
+      <c r="O79" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P79" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="Q79" s="0" t="s">
+      <c r="Q79" s="1" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="n">
+      <c r="A80" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B80" s="0" t="n">
+      <c r="B80" s="1" t="n">
         <v>12655</v>
       </c>
-      <c r="C80" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D80" s="0" t="s">
+      <c r="C80" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E80" s="0" t="s">
+      <c r="E80" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="F80" s="0" t="n">
+      <c r="F80" s="1" t="n">
         <v>11434910</v>
       </c>
-      <c r="G80" s="0" t="n">
+      <c r="G80" s="1" t="n">
         <v>10138280</v>
       </c>
-      <c r="H80" s="0" t="n">
+      <c r="H80" s="1" t="n">
         <v>1296635</v>
       </c>
-      <c r="I80" s="0" t="n">
+      <c r="I80" s="1" t="n">
         <v>43800760000</v>
       </c>
-      <c r="J80" s="0" t="n">
+      <c r="J80" s="1" t="n">
         <v>28242220000</v>
       </c>
-      <c r="K80" s="0" t="n">
+      <c r="K80" s="1" t="n">
         <v>15577490000</v>
       </c>
-      <c r="L80" s="0" t="n">
+      <c r="L80" s="1" t="n">
         <v>173161300</v>
       </c>
-      <c r="M80" s="0" t="n">
+      <c r="M80" s="1" t="n">
         <v>20118730</v>
       </c>
-      <c r="N80" s="0" t="n">
+      <c r="N80" s="1" t="n">
         <v>193288000</v>
       </c>
-      <c r="O80" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P80" s="0" t="s">
+      <c r="O80" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P80" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="Q80" s="0" t="s">
+      <c r="Q80" s="1" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="n">
+      <c r="A81" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B81" s="0" t="n">
+      <c r="B81" s="1" t="n">
         <v>12460</v>
       </c>
-      <c r="C81" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D81" s="0" t="s">
+      <c r="C81" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="E81" s="0" t="s">
+      <c r="E81" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="F81" s="0" t="n">
+      <c r="F81" s="1" t="n">
         <v>11354300</v>
       </c>
-      <c r="G81" s="0" t="n">
+      <c r="G81" s="1" t="n">
         <v>10085640</v>
       </c>
-      <c r="H81" s="0" t="n">
+      <c r="H81" s="1" t="n">
         <v>1268665</v>
       </c>
-      <c r="I81" s="0" t="n">
+      <c r="I81" s="1" t="n">
         <v>44006950000</v>
       </c>
-      <c r="J81" s="0" t="n">
+      <c r="J81" s="1" t="n">
         <v>28426360000</v>
       </c>
-      <c r="K81" s="0" t="n">
+      <c r="K81" s="1" t="n">
         <v>15596760000</v>
       </c>
-      <c r="L81" s="0" t="n">
+      <c r="L81" s="1" t="n">
         <v>172292800</v>
       </c>
-      <c r="M81" s="0" t="n">
+      <c r="M81" s="1" t="n">
         <v>19678810</v>
       </c>
-      <c r="N81" s="0" t="n">
+      <c r="N81" s="1" t="n">
         <v>191978300</v>
       </c>
-      <c r="O81" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P81" s="0" t="s">
+      <c r="O81" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P81" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="Q81" s="0" t="s">
+      <c r="Q81" s="1" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="n">
+      <c r="A82" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B82" s="0" t="n">
+      <c r="B82" s="1" t="n">
         <v>12266</v>
       </c>
-      <c r="C82" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D82" s="0" t="s">
+      <c r="C82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="E82" s="0" t="s">
+      <c r="E82" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="F82" s="0" t="n">
+      <c r="F82" s="1" t="n">
         <v>11271200</v>
       </c>
-      <c r="G82" s="0" t="n">
+      <c r="G82" s="1" t="n">
         <v>10033160</v>
       </c>
-      <c r="H82" s="0" t="n">
+      <c r="H82" s="1" t="n">
         <v>1238035</v>
       </c>
-      <c r="I82" s="0" t="n">
+      <c r="I82" s="1" t="n">
         <v>44213510000</v>
       </c>
-      <c r="J82" s="0" t="n">
+      <c r="J82" s="1" t="n">
         <v>28607240000</v>
       </c>
-      <c r="K82" s="0" t="n">
+      <c r="K82" s="1" t="n">
         <v>15615620000</v>
       </c>
-      <c r="L82" s="0" t="n">
+      <c r="L82" s="1" t="n">
         <v>171384300</v>
       </c>
-      <c r="M82" s="0" t="n">
+      <c r="M82" s="1" t="n">
         <v>19245470</v>
       </c>
-      <c r="N82" s="0" t="n">
+      <c r="N82" s="1" t="n">
         <v>190624100</v>
       </c>
-      <c r="O82" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P82" s="0" t="s">
+      <c r="O82" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P82" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="Q82" s="0" t="s">
+      <c r="Q82" s="1" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="n">
+      <c r="A83" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B83" s="0" t="n">
+      <c r="B83" s="1" t="n">
         <v>12075</v>
       </c>
-      <c r="C83" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D83" s="0" t="s">
+      <c r="C83" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E83" s="0" t="s">
+      <c r="E83" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="F83" s="0" t="n">
+      <c r="F83" s="1" t="n">
         <v>11185630</v>
       </c>
-      <c r="G83" s="0" t="n">
+      <c r="G83" s="1" t="n">
         <v>9975408</v>
       </c>
-      <c r="H83" s="0" t="n">
+      <c r="H83" s="1" t="n">
         <v>1210218</v>
       </c>
-      <c r="I83" s="0" t="n">
+      <c r="I83" s="1" t="n">
         <v>44416520000</v>
       </c>
-      <c r="J83" s="0" t="n">
+      <c r="J83" s="1" t="n">
         <v>28784870000</v>
       </c>
-      <c r="K83" s="0" t="n">
+      <c r="K83" s="1" t="n">
         <v>15634080000</v>
       </c>
-      <c r="L83" s="0" t="n">
+      <c r="L83" s="1" t="n">
         <v>170415800</v>
       </c>
-      <c r="M83" s="0" t="n">
+      <c r="M83" s="1" t="n">
         <v>18818600</v>
       </c>
-      <c r="N83" s="0" t="n">
+      <c r="N83" s="1" t="n">
         <v>189226600</v>
       </c>
-      <c r="O83" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P83" s="0" t="s">
+      <c r="O83" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P83" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="Q83" s="0" t="s">
+      <c r="Q83" s="1" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="n">
+      <c r="A84" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B84" s="0" t="n">
+      <c r="B84" s="1" t="n">
         <v>11884</v>
       </c>
-      <c r="C84" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D84" s="0" t="s">
+      <c r="C84" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="E84" s="0" t="s">
+      <c r="E84" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="F84" s="0" t="n">
+      <c r="F84" s="1" t="n">
         <v>11300330</v>
       </c>
-      <c r="G84" s="0" t="n">
+      <c r="G84" s="1" t="n">
         <v>10098790</v>
       </c>
-      <c r="H84" s="0" t="n">
+      <c r="H84" s="1" t="n">
         <v>1201548</v>
       </c>
-      <c r="I84" s="0" t="n">
+      <c r="I84" s="1" t="n">
         <v>44619430000</v>
       </c>
-      <c r="J84" s="0" t="n">
+      <c r="J84" s="1" t="n">
         <v>28962500000</v>
       </c>
-      <c r="K84" s="0" t="n">
+      <c r="K84" s="1" t="n">
         <v>15652320000</v>
       </c>
-      <c r="L84" s="0" t="n">
+      <c r="L84" s="1" t="n">
         <v>172492900</v>
       </c>
-      <c r="M84" s="0" t="n">
+      <c r="M84" s="1" t="n">
         <v>18552300</v>
       </c>
-      <c r="N84" s="0" t="n">
+      <c r="N84" s="1" t="n">
         <v>191064600</v>
       </c>
-      <c r="O84" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P84" s="0" t="s">
+      <c r="O84" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P84" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="Q84" s="0" t="s">
+      <c r="Q84" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="n">
+      <c r="A85" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B85" s="0" t="n">
+      <c r="B85" s="1" t="n">
         <v>11696</v>
       </c>
-      <c r="C85" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D85" s="0" t="s">
+      <c r="C85" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="E85" s="0" t="s">
+      <c r="E85" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F85" s="0" t="n">
+      <c r="F85" s="1" t="n">
         <v>11210290</v>
       </c>
-      <c r="G85" s="0" t="n">
+      <c r="G85" s="1" t="n">
         <v>10038270</v>
       </c>
-      <c r="H85" s="0" t="n">
+      <c r="H85" s="1" t="n">
         <v>1172022</v>
       </c>
-      <c r="I85" s="0" t="n">
+      <c r="I85" s="1" t="n">
         <v>44818760000</v>
       </c>
-      <c r="J85" s="0" t="n">
+      <c r="J85" s="1" t="n">
         <v>29136910000</v>
       </c>
-      <c r="K85" s="0" t="n">
+      <c r="K85" s="1" t="n">
         <v>15670170000</v>
       </c>
-      <c r="L85" s="0" t="n">
+      <c r="L85" s="1" t="n">
         <v>171475600</v>
       </c>
-      <c r="M85" s="0" t="n">
+      <c r="M85" s="1" t="n">
         <v>18136250</v>
       </c>
-      <c r="N85" s="0" t="n">
+      <c r="N85" s="1" t="n">
         <v>189591800</v>
       </c>
-      <c r="O85" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P85" s="0" t="s">
+      <c r="O85" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P85" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="Q85" s="0" t="s">
+      <c r="Q85" s="1" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="n">
+      <c r="A86" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B86" s="0" t="n">
+      <c r="B86" s="1" t="n">
         <v>11509</v>
       </c>
-      <c r="C86" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D86" s="0" t="s">
+      <c r="C86" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E86" s="0" t="s">
+      <c r="E86" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="F86" s="0" t="n">
+      <c r="F86" s="1" t="n">
         <v>11117980</v>
       </c>
-      <c r="G86" s="0" t="n">
+      <c r="G86" s="1" t="n">
         <v>9972701</v>
       </c>
-      <c r="H86" s="0" t="n">
+      <c r="H86" s="1" t="n">
         <v>1145281</v>
       </c>
-      <c r="I86" s="0" t="n">
+      <c r="I86" s="1" t="n">
         <v>45014440000</v>
       </c>
-      <c r="J86" s="0" t="n">
+      <c r="J86" s="1" t="n">
         <v>29308140000</v>
       </c>
-      <c r="K86" s="0" t="n">
+      <c r="K86" s="1" t="n">
         <v>15687650000</v>
       </c>
-      <c r="L86" s="0" t="n">
+      <c r="L86" s="1" t="n">
         <v>170345900</v>
       </c>
-      <c r="M86" s="0" t="n">
+      <c r="M86" s="1" t="n">
         <v>17726520</v>
       </c>
-      <c r="N86" s="0" t="n">
+      <c r="N86" s="1" t="n">
         <v>188078200</v>
       </c>
-      <c r="O86" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P86" s="0" t="s">
+      <c r="O86" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P86" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="Q86" s="0" t="s">
+      <c r="Q86" s="1" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="n">
+      <c r="A87" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B87" s="0" t="n">
+      <c r="B87" s="1" t="n">
         <v>11323</v>
       </c>
-      <c r="C87" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D87" s="0" t="s">
+      <c r="C87" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E87" s="0" t="s">
+      <c r="E87" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="F87" s="0" t="n">
+      <c r="F87" s="1" t="n">
         <v>11023440</v>
       </c>
-      <c r="G87" s="0" t="n">
+      <c r="G87" s="1" t="n">
         <v>9904313</v>
       </c>
-      <c r="H87" s="0" t="n">
+      <c r="H87" s="1" t="n">
         <v>1119126</v>
       </c>
-      <c r="I87" s="0" t="n">
+      <c r="I87" s="1" t="n">
         <v>45206530000</v>
       </c>
-      <c r="J87" s="0" t="n">
+      <c r="J87" s="1" t="n">
         <v>29476210000</v>
       </c>
-      <c r="K87" s="0" t="n">
+      <c r="K87" s="1" t="n">
         <v>15704780000</v>
       </c>
-      <c r="L87" s="0" t="n">
+      <c r="L87" s="1" t="n">
         <v>169197800</v>
       </c>
-      <c r="M87" s="0" t="n">
+      <c r="M87" s="1" t="n">
         <v>17323040</v>
       </c>
-      <c r="N87" s="0" t="n">
+      <c r="N87" s="1" t="n">
         <v>186525400</v>
       </c>
-      <c r="O87" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P87" s="0" t="s">
+      <c r="O87" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P87" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="Q87" s="0" t="s">
+      <c r="Q87" s="1" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="n">
+      <c r="A88" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B88" s="0" t="n">
+      <c r="B88" s="1" t="n">
         <v>11139</v>
       </c>
-      <c r="C88" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D88" s="0" t="s">
+      <c r="C88" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="E88" s="0" t="s">
+      <c r="E88" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="F88" s="0" t="n">
+      <c r="F88" s="1" t="n">
         <v>10926690</v>
       </c>
-      <c r="G88" s="0" t="n">
+      <c r="G88" s="1" t="n">
         <v>9835332</v>
       </c>
-      <c r="H88" s="0" t="n">
+      <c r="H88" s="1" t="n">
         <v>1091359</v>
       </c>
-      <c r="I88" s="0" t="n">
+      <c r="I88" s="1" t="n">
         <v>45395040000</v>
       </c>
-      <c r="J88" s="0" t="n">
+      <c r="J88" s="1" t="n">
         <v>29641150000</v>
       </c>
-      <c r="K88" s="0" t="n">
+      <c r="K88" s="1" t="n">
         <v>15721540000</v>
       </c>
-      <c r="L88" s="0" t="n">
+      <c r="L88" s="1" t="n">
         <v>168013600</v>
       </c>
-      <c r="M88" s="0" t="n">
+      <c r="M88" s="1" t="n">
         <v>16925780</v>
       </c>
-      <c r="N88" s="0" t="n">
+      <c r="N88" s="1" t="n">
         <v>184933700</v>
       </c>
-      <c r="O88" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P88" s="0" t="s">
+      <c r="O88" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P88" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="Q88" s="0" t="s">
+      <c r="Q88" s="1" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="n">
+      <c r="A89" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B89" s="0" t="n">
+      <c r="B89" s="1" t="n">
         <v>10956</v>
       </c>
-      <c r="C89" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D89" s="0" t="s">
+      <c r="C89" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="E89" s="0" t="s">
+      <c r="E89" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="F89" s="0" t="n">
+      <c r="F89" s="1" t="n">
         <v>10894920</v>
       </c>
-      <c r="G89" s="0" t="n">
+      <c r="G89" s="1" t="n">
         <v>9763417</v>
       </c>
-      <c r="H89" s="0" t="n">
+      <c r="H89" s="1" t="n">
         <v>1131508</v>
       </c>
-      <c r="I89" s="0" t="n">
+      <c r="I89" s="1" t="n">
         <v>88208440000</v>
       </c>
-      <c r="J89" s="0" t="n">
+      <c r="J89" s="1" t="n">
         <v>57066850000</v>
       </c>
-      <c r="K89" s="0" t="n">
+      <c r="K89" s="1" t="n">
         <v>31196870000</v>
       </c>
-      <c r="L89" s="0" t="n">
+      <c r="L89" s="1" t="n">
         <v>166780600</v>
       </c>
-      <c r="M89" s="0" t="n">
+      <c r="M89" s="1" t="n">
         <v>17575630</v>
       </c>
-      <c r="N89" s="0" t="n">
+      <c r="N89" s="1" t="n">
         <v>184345300</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="n">
+      <c r="A90" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B90" s="0" t="n">
+      <c r="B90" s="1" t="n">
         <v>10767</v>
       </c>
-      <c r="C90" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D90" s="0" t="s">
+      <c r="C90" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="E90" s="0" t="s">
+      <c r="E90" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="F90" s="0" t="n">
+      <c r="F90" s="1" t="n">
         <v>10792860</v>
       </c>
-      <c r="G90" s="0" t="n">
+      <c r="G90" s="1" t="n">
         <v>9687550</v>
       </c>
-      <c r="H90" s="0" t="n">
+      <c r="H90" s="1" t="n">
         <v>1105307</v>
       </c>
-      <c r="I90" s="0" t="n">
+      <c r="I90" s="1" t="n">
         <v>88389900000</v>
       </c>
-      <c r="J90" s="0" t="n">
+      <c r="J90" s="1" t="n">
         <v>57248320000</v>
       </c>
-      <c r="K90" s="0" t="n">
+      <c r="K90" s="1" t="n">
         <v>31218010000</v>
       </c>
-      <c r="L90" s="0" t="n">
+      <c r="L90" s="1" t="n">
         <v>165499700</v>
       </c>
-      <c r="M90" s="0" t="n">
+      <c r="M90" s="1" t="n">
         <v>17168310</v>
       </c>
-      <c r="N90" s="0" t="n">
+      <c r="N90" s="1" t="n">
         <v>182657800</v>
       </c>
-      <c r="O90" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P90" s="0" t="s">
+      <c r="O90" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P90" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="Q90" s="0" t="s">
+      <c r="Q90" s="1" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="n">
+      <c r="A91" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B91" s="0" t="n">
+      <c r="B91" s="1" t="n">
         <v>10579</v>
       </c>
-      <c r="C91" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D91" s="0" t="s">
+      <c r="C91" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="E91" s="0" t="s">
+      <c r="E91" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F91" s="0" t="n">
+      <c r="F91" s="1" t="n">
         <v>10688750</v>
       </c>
-      <c r="G91" s="0" t="n">
+      <c r="G91" s="1" t="n">
         <v>9610882</v>
       </c>
-      <c r="H91" s="0" t="n">
+      <c r="H91" s="1" t="n">
         <v>1077871</v>
       </c>
-      <c r="I91" s="0" t="n">
+      <c r="I91" s="1" t="n">
         <v>88567890000</v>
       </c>
-      <c r="J91" s="0" t="n">
+      <c r="J91" s="1" t="n">
         <v>57426300000</v>
       </c>
-      <c r="K91" s="0" t="n">
+      <c r="K91" s="1" t="n">
         <v>31238750000</v>
       </c>
-      <c r="L91" s="0" t="n">
+      <c r="L91" s="1" t="n">
         <v>164156500</v>
       </c>
-      <c r="M91" s="0" t="n">
+      <c r="M91" s="1" t="n">
         <v>16767400</v>
       </c>
-      <c r="N91" s="0" t="n">
+      <c r="N91" s="1" t="n">
         <v>180934100</v>
       </c>
-      <c r="O91" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P91" s="0" t="s">
+      <c r="O91" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P91" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="Q91" s="0" t="s">
+      <c r="Q91" s="1" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="n">
+      <c r="A92" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B92" s="0" t="n">
+      <c r="B92" s="1" t="n">
         <v>10393</v>
       </c>
-      <c r="C92" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D92" s="0" t="s">
+      <c r="C92" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="E92" s="0" t="s">
+      <c r="E92" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="F92" s="0" t="n">
+      <c r="F92" s="1" t="n">
         <v>10582720</v>
       </c>
-      <c r="G92" s="0" t="n">
+      <c r="G92" s="1" t="n">
         <v>9530122</v>
       </c>
-      <c r="H92" s="0" t="n">
+      <c r="H92" s="1" t="n">
         <v>1052598</v>
       </c>
-      <c r="I92" s="0" t="n">
+      <c r="I92" s="1" t="n">
         <v>88742440000</v>
       </c>
-      <c r="J92" s="0" t="n">
+      <c r="J92" s="1" t="n">
         <v>57600860000</v>
       </c>
-      <c r="K92" s="0" t="n">
+      <c r="K92" s="1" t="n">
         <v>31259090000</v>
       </c>
-      <c r="L92" s="0" t="n">
+      <c r="L92" s="1" t="n">
         <v>162792100</v>
       </c>
-      <c r="M92" s="0" t="n">
+      <c r="M92" s="1" t="n">
         <v>16372810</v>
       </c>
-      <c r="N92" s="0" t="n">
+      <c r="N92" s="1" t="n">
         <v>179176300</v>
       </c>
-      <c r="O92" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P92" s="0" t="s">
+      <c r="O92" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P92" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="Q92" s="0" t="s">
+      <c r="Q92" s="1" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="n">
+      <c r="A93" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B93" s="0" t="n">
+      <c r="B93" s="1" t="n">
         <v>10208</v>
       </c>
-      <c r="C93" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D93" s="0" t="s">
+      <c r="C93" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="E93" s="0" t="s">
+      <c r="E93" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="F93" s="0" t="n">
+      <c r="F93" s="1" t="n">
         <v>10681700</v>
       </c>
-      <c r="G93" s="0" t="n">
+      <c r="G93" s="1" t="n">
         <v>9635219</v>
       </c>
-      <c r="H93" s="0" t="n">
+      <c r="H93" s="1" t="n">
         <v>1046476</v>
       </c>
-      <c r="I93" s="0" t="n">
+      <c r="I93" s="1" t="n">
         <v>88916990000</v>
       </c>
-      <c r="J93" s="0" t="n">
+      <c r="J93" s="1" t="n">
         <v>57775400000</v>
       </c>
-      <c r="K93" s="0" t="n">
+      <c r="K93" s="1" t="n">
         <v>31279080000</v>
       </c>
-      <c r="L93" s="0" t="n">
+      <c r="L93" s="1" t="n">
         <v>164609100</v>
       </c>
-      <c r="M93" s="0" t="n">
+      <c r="M93" s="1" t="n">
         <v>16131670</v>
       </c>
-      <c r="N93" s="0" t="n">
+      <c r="N93" s="1" t="n">
         <v>180743700</v>
       </c>
-      <c r="O93" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P93" s="0" t="s">
+      <c r="O93" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P93" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="Q93" s="0" t="s">
+      <c r="Q93" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="n">
+      <c r="A94" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B94" s="0" t="n">
+      <c r="B94" s="1" t="n">
         <v>10026</v>
       </c>
-      <c r="C94" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D94" s="0" t="s">
+      <c r="C94" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E94" s="0" t="s">
+      <c r="E94" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="F94" s="0" t="n">
+      <c r="F94" s="1" t="n">
         <v>10571860</v>
       </c>
-      <c r="G94" s="0" t="n">
+      <c r="G94" s="1" t="n">
         <v>9552351</v>
       </c>
-      <c r="H94" s="0" t="n">
+      <c r="H94" s="1" t="n">
         <v>1019506</v>
       </c>
-      <c r="I94" s="0" t="n">
+      <c r="I94" s="1" t="n">
         <v>89088140000</v>
       </c>
-      <c r="J94" s="0" t="n">
+      <c r="J94" s="1" t="n">
         <v>57946550000</v>
       </c>
-      <c r="K94" s="0" t="n">
+      <c r="K94" s="1" t="n">
         <v>31298680000</v>
       </c>
-      <c r="L94" s="0" t="n">
+      <c r="L94" s="1" t="n">
         <v>163175900</v>
       </c>
-      <c r="M94" s="0" t="n">
+      <c r="M94" s="1" t="n">
         <v>15747600</v>
       </c>
-      <c r="N94" s="0" t="n">
+      <c r="N94" s="1" t="n">
         <v>178921400</v>
       </c>
-      <c r="O94" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P94" s="0" t="s">
+      <c r="O94" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P94" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="Q94" s="0" t="s">
+      <c r="Q94" s="1" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="n">
+      <c r="A95" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B95" s="0" t="n">
+      <c r="B95" s="1" t="n">
         <v>9845</v>
       </c>
-      <c r="C95" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D95" s="0" t="s">
+      <c r="C95" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="E95" s="0" t="s">
+      <c r="E95" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="F95" s="0" t="n">
+      <c r="F95" s="1" t="n">
         <v>10460210</v>
       </c>
-      <c r="G95" s="0" t="n">
+      <c r="G95" s="1" t="n">
         <v>9465790</v>
       </c>
-      <c r="H95" s="0" t="n">
+      <c r="H95" s="1" t="n">
         <v>994418</v>
       </c>
-      <c r="I95" s="0" t="n">
+      <c r="I95" s="1" t="n">
         <v>89255900000</v>
       </c>
-      <c r="J95" s="0" t="n">
+      <c r="J95" s="1" t="n">
         <v>58114320000</v>
       </c>
-      <c r="K95" s="0" t="n">
+      <c r="K95" s="1" t="n">
         <v>31317900000</v>
       </c>
-      <c r="L95" s="0" t="n">
+      <c r="L95" s="1" t="n">
         <v>161706700</v>
       </c>
-      <c r="M95" s="0" t="n">
+      <c r="M95" s="1" t="n">
         <v>15369690</v>
       </c>
-      <c r="N95" s="0" t="n">
+      <c r="N95" s="1" t="n">
         <v>177067100</v>
       </c>
-      <c r="O95" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P95" s="0" t="s">
+      <c r="O95" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P95" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="Q95" s="0" t="s">
+      <c r="Q95" s="1" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="n">
+      <c r="A96" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B96" s="0" t="n">
+      <c r="B96" s="1" t="n">
         <v>9665</v>
       </c>
-      <c r="C96" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D96" s="0" t="s">
+      <c r="C96" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="E96" s="0" t="s">
+      <c r="E96" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="F96" s="0" t="n">
+      <c r="F96" s="1" t="n">
         <v>10346760</v>
       </c>
-      <c r="G96" s="0" t="n">
+      <c r="G96" s="1" t="n">
         <v>9378462</v>
       </c>
-      <c r="H96" s="0" t="n">
+      <c r="H96" s="1" t="n">
         <v>968302</v>
       </c>
-      <c r="I96" s="0" t="n">
+      <c r="I96" s="1" t="n">
         <v>89420340000</v>
       </c>
-      <c r="J96" s="0" t="n">
+      <c r="J96" s="1" t="n">
         <v>58278760000</v>
       </c>
-      <c r="K96" s="0" t="n">
+      <c r="K96" s="1" t="n">
         <v>31336740000</v>
       </c>
-      <c r="L96" s="0" t="n">
+      <c r="L96" s="1" t="n">
         <v>160190300</v>
       </c>
-      <c r="M96" s="0" t="n">
+      <c r="M96" s="1" t="n">
         <v>14997880</v>
       </c>
-      <c r="N96" s="0" t="n">
+      <c r="N96" s="1" t="n">
         <v>175181600</v>
       </c>
-      <c r="O96" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P96" s="0" t="s">
+      <c r="O96" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P96" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="Q96" s="0" t="s">
+      <c r="Q96" s="1" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="n">
+      <c r="A97" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B97" s="0" t="n">
+      <c r="B97" s="1" t="n">
         <v>9488</v>
       </c>
-      <c r="C97" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D97" s="0" t="s">
+      <c r="C97" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="E97" s="0" t="s">
+      <c r="E97" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="F97" s="0" t="n">
+      <c r="F97" s="1" t="n">
         <v>10231630</v>
       </c>
-      <c r="G97" s="0" t="n">
+      <c r="G97" s="1" t="n">
         <v>9286864</v>
       </c>
-      <c r="H97" s="0" t="n">
+      <c r="H97" s="1" t="n">
         <v>944761</v>
       </c>
-      <c r="I97" s="0" t="n">
+      <c r="I97" s="1" t="n">
         <v>89581460000</v>
       </c>
-      <c r="J97" s="0" t="n">
+      <c r="J97" s="1" t="n">
         <v>58439880000</v>
       </c>
-      <c r="K97" s="0" t="n">
+      <c r="K97" s="1" t="n">
         <v>31355200000</v>
       </c>
-      <c r="L97" s="0" t="n">
+      <c r="L97" s="1" t="n">
         <v>158623800</v>
       </c>
-      <c r="M97" s="0" t="n">
+      <c r="M97" s="1" t="n">
         <v>14632150</v>
       </c>
-      <c r="N97" s="0" t="n">
+      <c r="N97" s="1" t="n">
         <v>173265800</v>
       </c>
-      <c r="O97" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P97" s="0" t="s">
+      <c r="O97" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P97" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="Q97" s="0" t="s">
+      <c r="Q97" s="1" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="n">
+      <c r="A98" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B98" s="0" t="n">
+      <c r="B98" s="1" t="n">
         <v>9312</v>
       </c>
-      <c r="C98" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D98" s="0" t="s">
+      <c r="C98" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E98" s="0" t="s">
+      <c r="E98" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="F98" s="0" t="n">
+      <c r="F98" s="1" t="n">
         <v>10114850</v>
       </c>
-      <c r="G98" s="0" t="n">
+      <c r="G98" s="1" t="n">
         <v>9192858</v>
       </c>
-      <c r="H98" s="0" t="n">
+      <c r="H98" s="1" t="n">
         <v>921991</v>
       </c>
-      <c r="I98" s="0" t="n">
+      <c r="I98" s="1" t="n">
         <v>89739320000</v>
       </c>
-      <c r="J98" s="0" t="n">
+      <c r="J98" s="1" t="n">
         <v>58597740000</v>
       </c>
-      <c r="K98" s="0" t="n">
+      <c r="K98" s="1" t="n">
         <v>31373290000</v>
       </c>
-      <c r="L98" s="0" t="n">
+      <c r="L98" s="1" t="n">
         <v>157069200</v>
       </c>
-      <c r="M98" s="0" t="n">
+      <c r="M98" s="1" t="n">
         <v>14272500</v>
       </c>
-      <c r="N98" s="0" t="n">
+      <c r="N98" s="1" t="n">
         <v>171321800</v>
       </c>
-      <c r="O98" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P98" s="0" t="s">
+      <c r="O98" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P98" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="Q98" s="0" t="s">
+      <c r="Q98" s="1" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="n">
+      <c r="A99" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B99" s="0" t="n">
+      <c r="B99" s="1" t="n">
         <v>9137</v>
       </c>
-      <c r="C99" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D99" s="0" t="s">
+      <c r="C99" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E99" s="0" t="s">
+      <c r="E99" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="F99" s="0" t="n">
+      <c r="F99" s="1" t="n">
         <v>9996495</v>
       </c>
-      <c r="G99" s="0" t="n">
+      <c r="G99" s="1" t="n">
         <v>9099431</v>
       </c>
-      <c r="H99" s="0" t="n">
+      <c r="H99" s="1" t="n">
         <v>897064</v>
       </c>
-      <c r="I99" s="0" t="n">
+      <c r="I99" s="1" t="n">
         <v>89893940000</v>
       </c>
-      <c r="J99" s="0" t="n">
+      <c r="J99" s="1" t="n">
         <v>58752360000</v>
       </c>
-      <c r="K99" s="0" t="n">
+      <c r="K99" s="1" t="n">
         <v>31391030000</v>
       </c>
-      <c r="L99" s="0" t="n">
+      <c r="L99" s="1" t="n">
         <v>155428000</v>
       </c>
-      <c r="M99" s="0" t="n">
+      <c r="M99" s="1" t="n">
         <v>13918810</v>
       </c>
-      <c r="N99" s="0" t="n">
+      <c r="N99" s="1" t="n">
         <v>169348500</v>
       </c>
-      <c r="O99" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P99" s="0" t="s">
+      <c r="O99" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P99" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="Q99" s="0" t="s">
+      <c r="Q99" s="1" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="n">
+      <c r="A100" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B100" s="0" t="n">
+      <c r="B100" s="1" t="n">
         <v>8964</v>
       </c>
-      <c r="C100" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D100" s="0" t="s">
+      <c r="C100" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E100" s="0" t="s">
+      <c r="E100" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="F100" s="0" t="n">
+      <c r="F100" s="1" t="n">
         <v>9876591</v>
       </c>
-      <c r="G100" s="0" t="n">
+      <c r="G100" s="1" t="n">
         <v>9002113</v>
       </c>
-      <c r="H100" s="0" t="n">
+      <c r="H100" s="1" t="n">
         <v>874478</v>
       </c>
-      <c r="I100" s="0" t="n">
+      <c r="I100" s="1" t="n">
         <v>90045360000</v>
       </c>
-      <c r="J100" s="0" t="n">
+      <c r="J100" s="1" t="n">
         <v>58903770000</v>
       </c>
-      <c r="K100" s="0" t="n">
+      <c r="K100" s="1" t="n">
         <v>31408390000</v>
       </c>
-      <c r="L100" s="0" t="n">
+      <c r="L100" s="1" t="n">
         <v>153780000</v>
       </c>
-      <c r="M100" s="0" t="n">
+      <c r="M100" s="1" t="n">
         <v>13571050</v>
       </c>
-      <c r="N100" s="0" t="n">
+      <c r="N100" s="1" t="n">
         <v>167348800</v>
       </c>
-      <c r="O100" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="P100" s="0" t="s">
+      <c r="O100" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="P100" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="Q100" s="0" t="s">
+      <c r="Q100" s="1" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="n">
+      <c r="A101" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B101" s="0" t="n">
+      <c r="B101" s="1" t="n">
         <v>8793</v>
       </c>
-      <c r="C101" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D101" s="0" t="s">
+      <c r="C101" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="E101" s="0" t="s">
+      <c r="E101" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="F101" s="0" t="n">
+      <c r="F101" s="1" t="n">
         <v>9807607</v>
       </c>
-      <c r="G101" s="0" t="n">
+      <c r="G101" s="1" t="n">
         <v>8903321</v>
       </c>
-      <c r="H101" s="0" t="n">
+      <c r="H101" s="1" t="n">
         <v>904286</v>
       </c>
-      <c r="I101" s="0" t="n">
+      <c r="I101" s="1" t="n">
         <v>178217100000</v>
       </c>
-      <c r="J101" s="0" t="n">
+      <c r="J101" s="1" t="n">
         <v>115933900000</v>
       </c>
-      <c r="K101" s="0" t="n">
+      <c r="K101" s="1" t="n">
         <v>62586770000</v>
       </c>
-      <c r="L101" s="0" t="n">
+      <c r="L101" s="1" t="n">
         <v>152090700</v>
       </c>
-      <c r="M101" s="0" t="n">
+      <c r="M101" s="1" t="n">
         <v>14042230</v>
       </c>
-      <c r="N101" s="0" t="n">
+      <c r="N101" s="1" t="n">
         <v>166136200</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+      <c r="A102" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B102" s="0" t="n">
+      <c r="B102" s="1" t="n">
         <f aca="false">SUM(B2:B101)</f>
         <v>1966932</v>
       </c>
-      <c r="C102" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D102" s="0" t="s">
+      <c r="C102" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="E102" s="0" t="s">
+      <c r="E102" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="F102" s="0" t="n">
+      <c r="F102" s="1" t="n">
         <f aca="false">SUM(F2:F101)</f>
         <v>1019700842</v>
       </c>
-      <c r="G102" s="0" t="n">
+      <c r="G102" s="1" t="n">
         <f aca="false">SUM(G2:G101)</f>
         <v>789675012</v>
       </c>
-      <c r="H102" s="0" t="n">
+      <c r="H102" s="1" t="n">
         <f aca="false">SUM(H2:H101)</f>
         <v>230025874</v>
       </c>
-      <c r="I102" s="0" t="n">
+      <c r="I102" s="1" t="n">
         <f aca="false">SUM(I2:I101)</f>
         <v>2460733335890</v>
       </c>
-      <c r="J102" s="0" t="n">
+      <c r="J102" s="1" t="n">
         <f aca="false">SUM(J2:J101)</f>
         <v>1576469939370</v>
       </c>
-      <c r="K102" s="0" t="n">
+      <c r="K102" s="1" t="n">
         <f aca="false">SUM(K2:K101)</f>
         <v>887617296290</v>
       </c>
-      <c r="L102" s="0" t="n">
+      <c r="L102" s="1" t="n">
         <f aca="false">SUM(L2:L101)</f>
         <v>13489511890</v>
       </c>
-      <c r="M102" s="0" t="n">
+      <c r="M102" s="1" t="n">
         <f aca="false">SUM(M2:M101)</f>
         <v>3570762140</v>
       </c>
-      <c r="N102" s="0" t="n">
+      <c r="N102" s="1" t="n">
         <f aca="false">SUM(N2:N101)</f>
         <v>17060198250</v>
       </c>
